--- a/research/traditional_assets/database/data/italy/italy_shoe.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_shoe.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1091721047521724</v>
+        <v>0.1089442917007672</v>
       </c>
       <c r="C2">
-        <v>509.8690735919826</v>
+        <v>506.2471247473538</v>
       </c>
       <c r="D2">
-        <v>494.8690735919826</v>
+        <v>496.6544706669124</v>
       </c>
       <c r="E2">
-        <v>-394.6345919558586</v>
+        <v>-389.2272460363001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.407345919558586</v>
       </c>
       <c r="G2">
         <v>15</v>
@@ -1439,28 +1439,28 @@
         <v>27.04</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2719894997537969</v>
       </c>
       <c r="N2">
-        <v>27.04</v>
+        <v>26.76801050024621</v>
       </c>
       <c r="O2">
-        <v>6.4896</v>
+        <v>6.424322520059089</v>
       </c>
       <c r="P2">
-        <v>20.5504</v>
+        <v>20.34368798018712</v>
       </c>
       <c r="Q2">
-        <v>20.7904</v>
+        <v>20.58368798018711</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1091721047521724</v>
+        <v>0.1096585976775426</v>
       </c>
       <c r="T2">
-        <v>0.872340875489653</v>
+        <v>0.8790376337257352</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>99.41560253052575</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1089442917007672</v>
+        <v>0.108716478649362</v>
       </c>
       <c r="C3">
-        <v>506.2471247473538</v>
+        <v>502.6381053216734</v>
       </c>
       <c r="D3">
-        <v>496.6544706669124</v>
+        <v>498.4527971607907</v>
       </c>
       <c r="E3">
-        <v>-389.2272460363001</v>
+        <v>-383.8199001167415</v>
       </c>
       <c r="F3">
-        <v>5.407345919558586</v>
+        <v>10.81469183911717</v>
       </c>
       <c r="G3">
         <v>15</v>
@@ -1521,28 +1521,28 @@
         <v>27.04</v>
       </c>
       <c r="M3">
-        <v>0.2719894997537969</v>
+        <v>0.5439789995075938</v>
       </c>
       <c r="N3">
-        <v>26.76801050024621</v>
+        <v>26.49602100049241</v>
       </c>
       <c r="O3">
-        <v>6.424322520059089</v>
+        <v>6.359045040118178</v>
       </c>
       <c r="P3">
-        <v>20.34368798018712</v>
+        <v>20.13697596037423</v>
       </c>
       <c r="Q3">
-        <v>20.58368798018711</v>
+        <v>20.37697596037423</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1096585976775426</v>
+        <v>0.1101550190299612</v>
       </c>
       <c r="T3">
-        <v>0.8790376337257352</v>
+        <v>0.8858710604972476</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>99.41560253052575</v>
+        <v>49.70780126526287</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.108716478649362</v>
+        <v>0.1084886655979568</v>
       </c>
       <c r="C4">
-        <v>502.6381053216734</v>
+        <v>499.0421562729771</v>
       </c>
       <c r="D4">
-        <v>498.4527971607907</v>
+        <v>500.2641940316529</v>
       </c>
       <c r="E4">
-        <v>-383.8199001167415</v>
+        <v>-378.4125541971829</v>
       </c>
       <c r="F4">
-        <v>10.81469183911717</v>
+        <v>16.22203775867576</v>
       </c>
       <c r="G4">
         <v>15</v>
@@ -1603,28 +1603,28 @@
         <v>27.04</v>
       </c>
       <c r="M4">
-        <v>0.5439789995075938</v>
+        <v>0.8159684992613906</v>
       </c>
       <c r="N4">
-        <v>26.49602100049241</v>
+        <v>26.22403150073861</v>
       </c>
       <c r="O4">
-        <v>6.359045040118178</v>
+        <v>6.293767560177266</v>
       </c>
       <c r="P4">
-        <v>20.13697596037423</v>
+        <v>19.93026394056135</v>
       </c>
       <c r="Q4">
-        <v>20.37697596037423</v>
+        <v>20.17026394056134</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1101550190299612</v>
+        <v>0.1106616758741822</v>
       </c>
       <c r="T4">
-        <v>0.8858710604972476</v>
+        <v>0.8928453826661109</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>49.70780126526287</v>
+        <v>33.13853417684192</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1084886655979568</v>
+        <v>0.1082608525465516</v>
       </c>
       <c r="C5">
-        <v>499.0421562729771</v>
+        <v>495.4594206157614</v>
       </c>
       <c r="D5">
-        <v>500.2641940316529</v>
+        <v>502.0888042939957</v>
       </c>
       <c r="E5">
-        <v>-378.4125541971829</v>
+        <v>-373.0052082776243</v>
       </c>
       <c r="F5">
-        <v>16.22203775867576</v>
+        <v>21.62938367823434</v>
       </c>
       <c r="G5">
         <v>15</v>
@@ -1685,28 +1685,28 @@
         <v>27.04</v>
       </c>
       <c r="M5">
-        <v>0.8159684992613906</v>
+        <v>1.087957999015188</v>
       </c>
       <c r="N5">
-        <v>26.22403150073861</v>
+        <v>25.95204200098481</v>
       </c>
       <c r="O5">
-        <v>6.293767560177266</v>
+        <v>6.228490080236355</v>
       </c>
       <c r="P5">
-        <v>19.93026394056135</v>
+        <v>19.72355192074846</v>
       </c>
       <c r="Q5">
-        <v>20.17026394056134</v>
+        <v>19.96355192074846</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1106616758741822</v>
+        <v>0.1111788880693245</v>
       </c>
       <c r="T5">
-        <v>0.8928453826661109</v>
+        <v>0.899965003213492</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.13853417684192</v>
+        <v>24.85390063263144</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1082608525465516</v>
+        <v>0.1080330394951464</v>
       </c>
       <c r="C6">
-        <v>495.4594206157614</v>
+        <v>491.8900434586241</v>
       </c>
       <c r="D6">
-        <v>502.0888042939957</v>
+        <v>503.9267730564169</v>
       </c>
       <c r="E6">
-        <v>-373.0052082776243</v>
+        <v>-367.5978623580657</v>
       </c>
       <c r="F6">
-        <v>21.62938367823434</v>
+        <v>27.03672959779293</v>
       </c>
       <c r="G6">
         <v>15</v>
@@ -1767,28 +1767,28 @@
         <v>27.04</v>
       </c>
       <c r="M6">
-        <v>1.087957999015188</v>
+        <v>1.359947498768984</v>
       </c>
       <c r="N6">
-        <v>25.95204200098481</v>
+        <v>25.68005250123102</v>
       </c>
       <c r="O6">
-        <v>6.228490080236355</v>
+        <v>6.163212600295444</v>
       </c>
       <c r="P6">
-        <v>19.72355192074846</v>
+        <v>19.51683990093557</v>
       </c>
       <c r="Q6">
-        <v>19.96355192074846</v>
+        <v>19.75683990093557</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1111788880693245</v>
+        <v>0.1117069889422593</v>
       </c>
       <c r="T6">
-        <v>0.899965003213492</v>
+        <v>0.9072345105092392</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.85390063263144</v>
+        <v>19.88312050610515</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1080330394951464</v>
+        <v>0.1078052264437411</v>
       </c>
       <c r="C7">
-        <v>491.8900434586241</v>
+        <v>488.3341720427337</v>
       </c>
       <c r="D7">
-        <v>503.9267730564169</v>
+        <v>505.7782475600852</v>
       </c>
       <c r="E7">
-        <v>-367.5978623580657</v>
+        <v>-362.1905164385071</v>
       </c>
       <c r="F7">
-        <v>27.03672959779293</v>
+        <v>32.44407551735152</v>
       </c>
       <c r="G7">
         <v>15</v>
@@ -1849,28 +1849,28 @@
         <v>27.04</v>
       </c>
       <c r="M7">
-        <v>1.359947498768984</v>
+        <v>1.631936998522781</v>
       </c>
       <c r="N7">
-        <v>25.68005250123102</v>
+        <v>25.40806300147722</v>
       </c>
       <c r="O7">
-        <v>6.163212600295444</v>
+        <v>6.097935120354533</v>
       </c>
       <c r="P7">
-        <v>19.51683990093557</v>
+        <v>19.31012788112269</v>
       </c>
       <c r="Q7">
-        <v>19.75683990093557</v>
+        <v>19.55012788112269</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1117069889422593</v>
+        <v>0.1122463260039799</v>
       </c>
       <c r="T7">
-        <v>0.9072345105092392</v>
+        <v>0.9146586881729809</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.88312050610515</v>
+        <v>16.56926708842096</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1078052264437411</v>
+        <v>0.1075774133923359</v>
       </c>
       <c r="C8">
-        <v>488.3341720427337</v>
+        <v>484.7919557811505</v>
       </c>
       <c r="D8">
-        <v>505.7782475600852</v>
+        <v>507.6433772180605</v>
       </c>
       <c r="E8">
-        <v>-362.1905164385071</v>
+        <v>-356.7831705189485</v>
       </c>
       <c r="F8">
-        <v>32.44407551735151</v>
+        <v>37.8514214369101</v>
       </c>
       <c r="G8">
         <v>15</v>
@@ -1931,28 +1931,28 @@
         <v>27.04</v>
       </c>
       <c r="M8">
-        <v>1.631936998522781</v>
+        <v>1.903926498276578</v>
       </c>
       <c r="N8">
-        <v>25.40806300147722</v>
+        <v>25.13607350172342</v>
       </c>
       <c r="O8">
-        <v>6.097935120354533</v>
+        <v>6.032657640413621</v>
       </c>
       <c r="P8">
-        <v>19.31012788112269</v>
+        <v>19.1034158613098</v>
       </c>
       <c r="Q8">
-        <v>19.55012788112269</v>
+        <v>19.3434158613098</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1122463260039799</v>
+        <v>0.1127972617121892</v>
       </c>
       <c r="T8">
-        <v>0.9146586881729809</v>
+        <v>0.9222425255714266</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.56926708842096</v>
+        <v>14.20222893293225</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1075774133923359</v>
+        <v>0.1074408003409307</v>
       </c>
       <c r="C9">
-        <v>484.7919557811504</v>
+        <v>480.5096879008748</v>
       </c>
       <c r="D9">
-        <v>507.6433772180606</v>
+        <v>508.7684552573434</v>
       </c>
       <c r="E9">
-        <v>-356.7831705189485</v>
+        <v>-351.3758245993899</v>
       </c>
       <c r="F9">
-        <v>37.85142143691011</v>
+        <v>43.25876735646869</v>
       </c>
       <c r="G9">
         <v>15</v>
@@ -2013,45 +2013,45 @@
         <v>27.04</v>
       </c>
       <c r="M9">
-        <v>1.903926498276578</v>
+        <v>2.240804149065078</v>
       </c>
       <c r="N9">
-        <v>25.13607350172342</v>
+        <v>24.79919585093493</v>
       </c>
       <c r="O9">
-        <v>6.032657640413621</v>
+        <v>5.951807004224382</v>
       </c>
       <c r="P9">
-        <v>19.1034158613098</v>
+        <v>18.84738884671054</v>
       </c>
       <c r="Q9">
-        <v>19.3434158613098</v>
+        <v>19.08738884671054</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1127972617121892</v>
+        <v>0.1133601742836203</v>
       </c>
       <c r="T9">
-        <v>0.9222425255714266</v>
+        <v>0.9299912290002734</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.24</v>
       </c>
       <c r="W9">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>14.20222893293225</v>
+        <v>12.06709654267723</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1074408003409307</v>
+        <v>0.1072243872895255</v>
       </c>
       <c r="C10">
-        <v>480.5096879008748</v>
+        <v>476.8948569532927</v>
       </c>
       <c r="D10">
-        <v>508.7684552573434</v>
+        <v>510.56097022932</v>
       </c>
       <c r="E10">
-        <v>-351.3758245993899</v>
+        <v>-345.9684786798314</v>
       </c>
       <c r="F10">
-        <v>43.25876735646869</v>
+        <v>48.66611327602727</v>
       </c>
       <c r="G10">
         <v>15</v>
@@ -2095,28 +2095,28 @@
         <v>27.04</v>
       </c>
       <c r="M10">
-        <v>2.240804149065078</v>
+        <v>2.520904667698213</v>
       </c>
       <c r="N10">
-        <v>24.79919585093493</v>
+        <v>24.51909533230179</v>
       </c>
       <c r="O10">
-        <v>5.951807004224382</v>
+        <v>5.884582879752429</v>
       </c>
       <c r="P10">
-        <v>18.84738884671054</v>
+        <v>18.63451245254936</v>
       </c>
       <c r="Q10">
-        <v>19.08738884671054</v>
+        <v>18.87451245254936</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1133601742836203</v>
+        <v>0.1139354585599181</v>
       </c>
       <c r="T10">
-        <v>0.9299912290002734</v>
+        <v>0.9379102336033807</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.06709654267723</v>
+        <v>10.72630803793532</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1072243872895255</v>
+        <v>0.1071371742381203</v>
       </c>
       <c r="C11">
-        <v>476.8948569532927</v>
+        <v>472.2134587268775</v>
       </c>
       <c r="D11">
-        <v>510.56097022932</v>
+        <v>511.2869179224634</v>
       </c>
       <c r="E11">
-        <v>-345.9684786798314</v>
+        <v>-340.5611327602728</v>
       </c>
       <c r="F11">
-        <v>48.66611327602727</v>
+        <v>54.07345919558585</v>
       </c>
       <c r="G11">
         <v>15</v>
@@ -2177,45 +2177,45 @@
         <v>27.04</v>
       </c>
       <c r="M11">
-        <v>2.520904667698213</v>
+        <v>2.892930066963843</v>
       </c>
       <c r="N11">
-        <v>24.51909533230179</v>
+        <v>24.14706993303616</v>
       </c>
       <c r="O11">
-        <v>5.884582879752429</v>
+        <v>5.795296783928678</v>
       </c>
       <c r="P11">
-        <v>18.63451245254936</v>
+        <v>18.35177314910748</v>
       </c>
       <c r="Q11">
-        <v>18.87451245254936</v>
+        <v>18.59177314910748</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1139354585599181</v>
+        <v>0.1145235269312448</v>
       </c>
       <c r="T11">
-        <v>0.9379102336033807</v>
+        <v>0.9460052160865571</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.24</v>
       </c>
       <c r="W11">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.72630803793532</v>
+        <v>9.346924873430741</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1071371742381203</v>
+        <v>0.1069336811867151</v>
       </c>
       <c r="C12">
-        <v>472.2134587268775</v>
+        <v>468.5080115487644</v>
       </c>
       <c r="D12">
-        <v>511.2869179224634</v>
+        <v>512.9888166639089</v>
       </c>
       <c r="E12">
-        <v>-340.5611327602728</v>
+        <v>-335.1537868407142</v>
       </c>
       <c r="F12">
-        <v>54.07345919558586</v>
+        <v>59.48080511514445</v>
       </c>
       <c r="G12">
         <v>15</v>
@@ -2259,28 +2259,28 @@
         <v>27.04</v>
       </c>
       <c r="M12">
-        <v>2.892930066963844</v>
+        <v>3.182223073660228</v>
       </c>
       <c r="N12">
-        <v>24.14706993303616</v>
+        <v>23.85777692633977</v>
       </c>
       <c r="O12">
-        <v>5.795296783928678</v>
+        <v>5.725866462321545</v>
       </c>
       <c r="P12">
-        <v>18.35177314910748</v>
+        <v>18.13191046401823</v>
       </c>
       <c r="Q12">
-        <v>18.59177314910748</v>
+        <v>18.37191046401823</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1145235269312448</v>
+        <v>0.1151248103221518</v>
       </c>
       <c r="T12">
-        <v>0.9460052160865571</v>
+        <v>0.9542821082884564</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.346924873430739</v>
+        <v>8.49720443039158</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1069336811867151</v>
+        <v>0.1067301881353099</v>
       </c>
       <c r="C13">
-        <v>468.5080115487644</v>
+        <v>464.8139322846097</v>
       </c>
       <c r="D13">
-        <v>512.9888166639089</v>
+        <v>514.7020833193127</v>
       </c>
       <c r="E13">
-        <v>-335.1537868407142</v>
+        <v>-329.7464409211556</v>
       </c>
       <c r="F13">
-        <v>59.48080511514445</v>
+        <v>64.88815103470303</v>
       </c>
       <c r="G13">
         <v>15</v>
@@ -2341,28 +2341,28 @@
         <v>27.04</v>
       </c>
       <c r="M13">
-        <v>3.182223073660228</v>
+        <v>3.471516080356612</v>
       </c>
       <c r="N13">
-        <v>23.85777692633977</v>
+        <v>23.56848391964339</v>
       </c>
       <c r="O13">
-        <v>5.725866462321545</v>
+        <v>5.656436140714414</v>
       </c>
       <c r="P13">
-        <v>18.13191046401823</v>
+        <v>17.91204777892898</v>
       </c>
       <c r="Q13">
-        <v>18.37191046401823</v>
+        <v>18.15204777892898</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1151248103221518</v>
+        <v>0.1157397592446703</v>
       </c>
       <c r="T13">
-        <v>0.9542821082884564</v>
+        <v>0.9627471116767624</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.49720443039158</v>
+        <v>7.789104061192283</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1067301881353099</v>
+        <v>0.1066057350839046</v>
       </c>
       <c r="C14">
-        <v>464.8139322846097</v>
+        <v>460.4600436539945</v>
       </c>
       <c r="D14">
-        <v>514.7020833193127</v>
+        <v>515.7555406082562</v>
       </c>
       <c r="E14">
-        <v>-329.7464409211556</v>
+        <v>-324.339095001597</v>
       </c>
       <c r="F14">
-        <v>64.88815103470303</v>
+        <v>70.29549695426162</v>
       </c>
       <c r="G14">
         <v>15</v>
@@ -2423,45 +2423,45 @@
         <v>27.04</v>
       </c>
       <c r="M14">
-        <v>3.471516080356612</v>
+        <v>3.817045484616406</v>
       </c>
       <c r="N14">
-        <v>23.56848391964339</v>
+        <v>23.2229545153836</v>
       </c>
       <c r="O14">
-        <v>5.656436140714414</v>
+        <v>5.573509083692063</v>
       </c>
       <c r="P14">
-        <v>17.91204777892898</v>
+        <v>17.64944543169153</v>
       </c>
       <c r="Q14">
-        <v>18.15204777892898</v>
+        <v>17.88944543169153</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1157397592446703</v>
+        <v>0.1163688449240283</v>
       </c>
       <c r="T14">
-        <v>0.9627471116767624</v>
+        <v>0.9714067128441102</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.24</v>
       </c>
       <c r="W14">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.789104061192283</v>
+        <v>7.084013043328296</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1066057350839046</v>
+        <v>0.1064083220324994</v>
       </c>
       <c r="C15">
-        <v>460.4600436539945</v>
+        <v>456.732613489174</v>
       </c>
       <c r="D15">
-        <v>515.7555406082562</v>
+        <v>517.4354563629942</v>
       </c>
       <c r="E15">
-        <v>-324.339095001597</v>
+        <v>-318.9317490820384</v>
       </c>
       <c r="F15">
-        <v>70.29549695426162</v>
+        <v>75.70284287382022</v>
       </c>
       <c r="G15">
         <v>15</v>
@@ -2505,28 +2505,28 @@
         <v>27.04</v>
       </c>
       <c r="M15">
-        <v>3.817045484616406</v>
+        <v>4.110664368048438</v>
       </c>
       <c r="N15">
-        <v>23.2229545153836</v>
+        <v>22.92933563195157</v>
       </c>
       <c r="O15">
-        <v>5.573509083692063</v>
+        <v>5.503040551668375</v>
       </c>
       <c r="P15">
-        <v>17.64944543169153</v>
+        <v>17.42629508028319</v>
       </c>
       <c r="Q15">
-        <v>17.88944543169153</v>
+        <v>17.66629508028319</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1163688449240283</v>
+        <v>0.1170125605029063</v>
       </c>
       <c r="T15">
-        <v>0.9714067128441102</v>
+        <v>0.9802677000851171</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.084013043328296</v>
+        <v>6.57801211166199</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1064083220324994</v>
+        <v>0.1062109089810942</v>
       </c>
       <c r="C16">
-        <v>456.732613489174</v>
+        <v>453.0161627087338</v>
       </c>
       <c r="D16">
-        <v>517.4354563629942</v>
+        <v>519.1263515021126</v>
       </c>
       <c r="E16">
-        <v>-318.9317490820384</v>
+        <v>-313.5244031624799</v>
       </c>
       <c r="F16">
-        <v>75.70284287382022</v>
+        <v>81.1101887933788</v>
       </c>
       <c r="G16">
         <v>15</v>
@@ -2587,28 +2587,28 @@
         <v>27.04</v>
       </c>
       <c r="M16">
-        <v>4.110664368048438</v>
+        <v>4.404283251480469</v>
       </c>
       <c r="N16">
-        <v>22.92933563195157</v>
+        <v>22.63571674851953</v>
       </c>
       <c r="O16">
-        <v>5.503040551668375</v>
+        <v>5.432572019644688</v>
       </c>
       <c r="P16">
-        <v>17.42629508028319</v>
+        <v>17.20314472887485</v>
       </c>
       <c r="Q16">
-        <v>17.66629508028319</v>
+        <v>17.44314472887485</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1170125605029063</v>
+        <v>0.1176714223306991</v>
       </c>
       <c r="T16">
-        <v>0.9802677000851171</v>
+        <v>0.9893371811435595</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.57801211166199</v>
+        <v>6.139477970884524</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1062109089810942</v>
+        <v>0.106135095929689</v>
       </c>
       <c r="C17">
-        <v>453.0161627087338</v>
+        <v>448.2611162869349</v>
       </c>
       <c r="D17">
-        <v>519.1263515021126</v>
+        <v>519.7786509998723</v>
       </c>
       <c r="E17">
-        <v>-313.5244031624799</v>
+        <v>-308.1170572429212</v>
       </c>
       <c r="F17">
-        <v>81.11018879337878</v>
+        <v>86.51753471293738</v>
       </c>
       <c r="G17">
         <v>15</v>
@@ -2669,45 +2669,45 @@
         <v>27.04</v>
       </c>
       <c r="M17">
-        <v>4.404283251480468</v>
+        <v>4.784419669625437</v>
       </c>
       <c r="N17">
-        <v>22.63571674851953</v>
+        <v>22.25558033037457</v>
       </c>
       <c r="O17">
-        <v>5.432572019644688</v>
+        <v>5.341339279289896</v>
       </c>
       <c r="P17">
-        <v>17.20314472887485</v>
+        <v>16.91424105108467</v>
       </c>
       <c r="Q17">
-        <v>17.44314472887485</v>
+        <v>17.15424105108467</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1176714223306991</v>
+        <v>0.1183459713448679</v>
       </c>
       <c r="T17">
-        <v>0.9893371811435593</v>
+        <v>0.9986226022272029</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.139477970884525</v>
+        <v>5.651678127583009</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.106135095929689</v>
+        <v>0.1059452828782838</v>
       </c>
       <c r="C18">
-        <v>448.2611162869349</v>
+        <v>444.4941445925878</v>
       </c>
       <c r="D18">
-        <v>519.7786509998723</v>
+        <v>521.4190252250837</v>
       </c>
       <c r="E18">
-        <v>-308.1170572429212</v>
+        <v>-302.7097113233627</v>
       </c>
       <c r="F18">
-        <v>86.51753471293738</v>
+        <v>91.92488063249597</v>
       </c>
       <c r="G18">
         <v>15</v>
@@ -2751,28 +2751,28 @@
         <v>27.04</v>
       </c>
       <c r="M18">
-        <v>4.784419669625437</v>
+        <v>5.083445898977027</v>
       </c>
       <c r="N18">
-        <v>22.25558033037457</v>
+        <v>21.95655410102297</v>
       </c>
       <c r="O18">
-        <v>5.341339279289896</v>
+        <v>5.269572984245514</v>
       </c>
       <c r="P18">
-        <v>16.91424105108467</v>
+        <v>16.68698111677746</v>
       </c>
       <c r="Q18">
-        <v>17.15424105108467</v>
+        <v>16.92698111677746</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1183459713448679</v>
+        <v>0.1190367745521491</v>
       </c>
       <c r="T18">
-        <v>0.9986226022272029</v>
+        <v>1.008131768397199</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.651678127583009</v>
+        <v>5.319226473019301</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1059452828782838</v>
+        <v>0.1057554698268786</v>
       </c>
       <c r="C19">
-        <v>444.4941445925878</v>
+        <v>440.7375594213726</v>
       </c>
       <c r="D19">
-        <v>521.4190252250837</v>
+        <v>523.0697859734272</v>
       </c>
       <c r="E19">
-        <v>-302.7097113233627</v>
+        <v>-297.3023654038041</v>
       </c>
       <c r="F19">
-        <v>91.92488063249597</v>
+        <v>97.33222655205456</v>
       </c>
       <c r="G19">
         <v>15</v>
@@ -2833,28 +2833,28 @@
         <v>27.04</v>
       </c>
       <c r="M19">
-        <v>5.083445898977027</v>
+        <v>5.382472128328618</v>
       </c>
       <c r="N19">
-        <v>21.95655410102297</v>
+        <v>21.65752787167138</v>
       </c>
       <c r="O19">
-        <v>5.269572984245514</v>
+        <v>5.197806689201132</v>
       </c>
       <c r="P19">
-        <v>16.68698111677746</v>
+        <v>16.45972118247025</v>
       </c>
       <c r="Q19">
-        <v>16.92698111677746</v>
+        <v>16.69972118247025</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1190367745521491</v>
+        <v>0.1197444266181446</v>
       </c>
       <c r="T19">
-        <v>1.008131768397199</v>
+        <v>1.01787286544939</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.319226473019301</v>
+        <v>5.023713891184895</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1057554698268786</v>
+        <v>0.1055656567754734</v>
       </c>
       <c r="C20">
-        <v>440.7375594213726</v>
+        <v>436.9914597346878</v>
       </c>
       <c r="D20">
-        <v>523.0697859734271</v>
+        <v>524.7310322063009</v>
       </c>
       <c r="E20">
-        <v>-297.3023654038041</v>
+        <v>-291.8950194842455</v>
       </c>
       <c r="F20">
-        <v>97.33222655205455</v>
+        <v>102.7395724716131</v>
       </c>
       <c r="G20">
         <v>15</v>
@@ -2915,28 +2915,28 @@
         <v>27.04</v>
       </c>
       <c r="M20">
-        <v>5.382472128328617</v>
+        <v>5.681498357680206</v>
       </c>
       <c r="N20">
-        <v>21.65752787167138</v>
+        <v>21.3585016423198</v>
       </c>
       <c r="O20">
-        <v>5.197806689201132</v>
+        <v>5.126040394156751</v>
       </c>
       <c r="P20">
-        <v>16.45972118247025</v>
+        <v>16.23246124816305</v>
       </c>
       <c r="Q20">
-        <v>16.69972118247025</v>
+        <v>16.47246124816305</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1197444266181446</v>
+        <v>0.1204695515746585</v>
       </c>
       <c r="T20">
-        <v>1.01787286544939</v>
+        <v>1.02785448341645</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.023713891184896</v>
+        <v>4.759307896912008</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1055656567754734</v>
+        <v>0.1053758437240681</v>
       </c>
       <c r="C21">
-        <v>436.9914597346878</v>
+        <v>433.2559457551251</v>
       </c>
       <c r="D21">
-        <v>524.7310322063009</v>
+        <v>526.4028641462968</v>
       </c>
       <c r="E21">
-        <v>-291.8950194842455</v>
+        <v>-286.4876735646869</v>
       </c>
       <c r="F21">
-        <v>102.7395724716131</v>
+        <v>108.1469183911717</v>
       </c>
       <c r="G21">
         <v>15</v>
@@ -2997,28 +2997,28 @@
         <v>27.04</v>
       </c>
       <c r="M21">
-        <v>5.681498357680206</v>
+        <v>5.980524587031796</v>
       </c>
       <c r="N21">
-        <v>21.3585016423198</v>
+        <v>21.0594754129682</v>
       </c>
       <c r="O21">
-        <v>5.126040394156751</v>
+        <v>5.054274099112368</v>
       </c>
       <c r="P21">
-        <v>16.23246124816305</v>
+        <v>16.00520131385584</v>
       </c>
       <c r="Q21">
-        <v>16.47246124816305</v>
+        <v>16.24520131385583</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1204695515746585</v>
+        <v>0.1212128046550852</v>
       </c>
       <c r="T21">
-        <v>1.02785448341645</v>
+        <v>1.038085641832687</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.759307896912008</v>
+        <v>4.521342502066406</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1053758437240681</v>
+        <v>0.1055850306726629</v>
       </c>
       <c r="C22">
-        <v>433.2559457551251</v>
+        <v>426.0067239070377</v>
       </c>
       <c r="D22">
-        <v>526.4028641462968</v>
+        <v>524.560988217768</v>
       </c>
       <c r="E22">
-        <v>-286.4876735646869</v>
+        <v>-281.0803276451283</v>
       </c>
       <c r="F22">
-        <v>108.1469183911717</v>
+        <v>113.5542643107303</v>
       </c>
       <c r="G22">
         <v>15</v>
@@ -3079,45 +3079,45 @@
         <v>27.04</v>
       </c>
       <c r="M22">
-        <v>5.980524587031796</v>
+        <v>6.563436477160213</v>
       </c>
       <c r="N22">
-        <v>21.0594754129682</v>
+        <v>20.47656352283979</v>
       </c>
       <c r="O22">
-        <v>5.054274099112368</v>
+        <v>4.914375245481549</v>
       </c>
       <c r="P22">
-        <v>16.00520131385584</v>
+        <v>15.56218827735824</v>
       </c>
       <c r="Q22">
-        <v>16.24520131385583</v>
+        <v>15.80218827735824</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1212128046550852</v>
+        <v>0.1219748742691936</v>
       </c>
       <c r="T22">
-        <v>1.038085641832687</v>
+        <v>1.048575816917689</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.521342502066406</v>
+        <v>4.119793052632596</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1055850306726629</v>
+        <v>0.1059994176212577</v>
       </c>
       <c r="C23">
-        <v>426.0067239070377</v>
+        <v>416.9885253272922</v>
       </c>
       <c r="D23">
-        <v>524.560988217768</v>
+        <v>520.9501355575811</v>
       </c>
       <c r="E23">
-        <v>-281.0803276451284</v>
+        <v>-275.6729817255697</v>
       </c>
       <c r="F23">
-        <v>113.5542643107303</v>
+        <v>118.9616102302889</v>
       </c>
       <c r="G23">
         <v>15</v>
@@ -3161,45 +3161,45 @@
         <v>27.04</v>
       </c>
       <c r="M23">
-        <v>6.563436477160212</v>
+        <v>7.292346707116709</v>
       </c>
       <c r="N23">
-        <v>20.47656352283979</v>
+        <v>19.74765329288329</v>
       </c>
       <c r="O23">
-        <v>4.914375245481549</v>
+        <v>4.73943679029199</v>
       </c>
       <c r="P23">
-        <v>15.56218827735824</v>
+        <v>15.0082165025913</v>
       </c>
       <c r="Q23">
-        <v>15.80218827735824</v>
+        <v>15.2482165025913</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1219748742691936</v>
+        <v>0.1227564841298176</v>
       </c>
       <c r="T23">
-        <v>1.048575816917689</v>
+        <v>1.059334970851025</v>
       </c>
       <c r="U23">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.119793052632597</v>
+        <v>3.707997039363373</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1059994176212577</v>
+        <v>0.1058552045698525</v>
       </c>
       <c r="C24">
-        <v>416.9885253272922</v>
+        <v>412.8321585562825</v>
       </c>
       <c r="D24">
-        <v>520.9501355575811</v>
+        <v>522.2011147061299</v>
       </c>
       <c r="E24">
-        <v>-275.6729817255697</v>
+        <v>-270.2656358060111</v>
       </c>
       <c r="F24">
-        <v>118.9616102302889</v>
+        <v>124.3689561498475</v>
       </c>
       <c r="G24">
         <v>15</v>
@@ -3243,28 +3243,28 @@
         <v>27.04</v>
       </c>
       <c r="M24">
-        <v>7.292346707116709</v>
+        <v>7.623817011985651</v>
       </c>
       <c r="N24">
-        <v>19.74765329288329</v>
+        <v>19.41618298801435</v>
       </c>
       <c r="O24">
-        <v>4.73943679029199</v>
+        <v>4.659883917123445</v>
       </c>
       <c r="P24">
-        <v>15.0082165025913</v>
+        <v>14.75629907089091</v>
       </c>
       <c r="Q24">
-        <v>15.2482165025913</v>
+        <v>14.99629907089091</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1227564841298176</v>
+        <v>0.123558395545263</v>
       </c>
       <c r="T24">
-        <v>1.059334970851025</v>
+        <v>1.070373583328083</v>
       </c>
       <c r="U24">
         <v>0.0613</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.707997039363373</v>
+        <v>3.546779776782357</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1058552045698525</v>
+        <v>0.1062217115184473</v>
       </c>
       <c r="C25">
-        <v>412.8321585562825</v>
+        <v>404.2572370700285</v>
       </c>
       <c r="D25">
-        <v>522.2011147061299</v>
+        <v>519.0335391394345</v>
       </c>
       <c r="E25">
-        <v>-270.2656358060111</v>
+        <v>-264.8582898864526</v>
       </c>
       <c r="F25">
-        <v>124.3689561498475</v>
+        <v>129.7763020694061</v>
       </c>
       <c r="G25">
         <v>15</v>
@@ -3325,45 +3325,45 @@
         <v>27.04</v>
       </c>
       <c r="M25">
-        <v>7.623817011985651</v>
+        <v>8.318660962648931</v>
       </c>
       <c r="N25">
-        <v>19.41618298801435</v>
+        <v>18.72133903735107</v>
       </c>
       <c r="O25">
-        <v>4.659883917123445</v>
+        <v>4.493121368964257</v>
       </c>
       <c r="P25">
-        <v>14.75629907089091</v>
+        <v>14.22821766838682</v>
       </c>
       <c r="Q25">
-        <v>14.99629907089091</v>
+        <v>14.46821766838681</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.123558395545263</v>
+        <v>0.1243814098926938</v>
       </c>
       <c r="T25">
-        <v>1.070373583328083</v>
+        <v>1.08170268560717</v>
       </c>
       <c r="U25">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.546779776782357</v>
+        <v>3.250523145661365</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1062217115184473</v>
+        <v>0.1060987784670421</v>
       </c>
       <c r="C26">
-        <v>404.2572370700286</v>
+        <v>399.9080614545822</v>
       </c>
       <c r="D26">
-        <v>519.0335391394347</v>
+        <v>520.0917094435468</v>
       </c>
       <c r="E26">
-        <v>-264.8582898864526</v>
+        <v>-259.450943966894</v>
       </c>
       <c r="F26">
-        <v>129.7763020694061</v>
+        <v>135.1836479889647</v>
       </c>
       <c r="G26">
         <v>15</v>
@@ -3407,28 +3407,28 @@
         <v>27.04</v>
       </c>
       <c r="M26">
-        <v>8.318660962648929</v>
+        <v>8.665271836092634</v>
       </c>
       <c r="N26">
-        <v>18.72133903735107</v>
+        <v>18.37472816390737</v>
       </c>
       <c r="O26">
-        <v>4.493121368964257</v>
+        <v>4.409934759337768</v>
       </c>
       <c r="P26">
-        <v>14.22821766838682</v>
+        <v>13.9647934045696</v>
       </c>
       <c r="Q26">
-        <v>14.46821766838681</v>
+        <v>14.2047934045696</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1243814098926938</v>
+        <v>0.1252263712893894</v>
       </c>
       <c r="T26">
-        <v>1.08170268560717</v>
+        <v>1.093333897280365</v>
       </c>
       <c r="U26">
         <v>0.0641</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.250523145661365</v>
+        <v>3.120502219834912</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1060987784670421</v>
+        <v>0.1059758454156369</v>
       </c>
       <c r="C27">
-        <v>399.9080614545822</v>
+        <v>395.5632093049214</v>
       </c>
       <c r="D27">
-        <v>520.0917094435468</v>
+        <v>521.1542032134447</v>
       </c>
       <c r="E27">
-        <v>-259.450943966894</v>
+        <v>-254.0435980473354</v>
       </c>
       <c r="F27">
-        <v>135.1836479889647</v>
+        <v>140.5909939085232</v>
       </c>
       <c r="G27">
         <v>15</v>
@@ -3489,28 +3489,28 @@
         <v>27.04</v>
       </c>
       <c r="M27">
-        <v>8.665271836092634</v>
+        <v>9.011882709536341</v>
       </c>
       <c r="N27">
-        <v>18.37472816390737</v>
+        <v>18.02811729046366</v>
       </c>
       <c r="O27">
-        <v>4.409934759337768</v>
+        <v>4.326748149711278</v>
       </c>
       <c r="P27">
-        <v>13.9647934045696</v>
+        <v>13.70136914075238</v>
       </c>
       <c r="Q27">
-        <v>14.2047934045696</v>
+        <v>13.94136914075238</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1252263712893894</v>
+        <v>0.1260941694805904</v>
       </c>
       <c r="T27">
-        <v>1.093333897280365</v>
+        <v>1.105279466025809</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.120502219834912</v>
+        <v>3.000482903687414</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1059758454156369</v>
+        <v>0.1074534723642316</v>
       </c>
       <c r="C28">
-        <v>395.5632093049214</v>
+        <v>377.6655450705686</v>
       </c>
       <c r="D28">
-        <v>521.1542032134447</v>
+        <v>508.6638848986505</v>
       </c>
       <c r="E28">
-        <v>-254.0435980473354</v>
+        <v>-248.6362521277768</v>
       </c>
       <c r="F28">
-        <v>140.5909939085232</v>
+        <v>145.9983398280818</v>
       </c>
       <c r="G28">
         <v>15</v>
@@ -3571,45 +3571,45 @@
         <v>27.04</v>
       </c>
       <c r="M28">
-        <v>9.011882709536341</v>
+        <v>10.49728063363908</v>
       </c>
       <c r="N28">
-        <v>18.02811729046366</v>
+        <v>16.54271936636092</v>
       </c>
       <c r="O28">
-        <v>4.326748149711278</v>
+        <v>3.970252647926621</v>
       </c>
       <c r="P28">
-        <v>13.70136914075238</v>
+        <v>12.5724667184343</v>
       </c>
       <c r="Q28">
-        <v>13.94136914075238</v>
+        <v>12.8124667184343</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1260941694805904</v>
+        <v>0.1269857429647009</v>
       </c>
       <c r="T28">
-        <v>1.105279466025809</v>
+        <v>1.117552310627292</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.000482903687414</v>
+        <v>2.575905221905654</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1074534723642316</v>
+        <v>0.1082197393128264</v>
       </c>
       <c r="C29">
-        <v>377.6655450705686</v>
+        <v>366.0138231373861</v>
       </c>
       <c r="D29">
-        <v>508.6638848986505</v>
+        <v>502.4195088850266</v>
       </c>
       <c r="E29">
-        <v>-248.6362521277768</v>
+        <v>-243.2289062082182</v>
       </c>
       <c r="F29">
-        <v>145.9983398280818</v>
+        <v>151.4056857476404</v>
       </c>
       <c r="G29">
         <v>15</v>
@@ -3653,45 +3653,45 @@
         <v>27.04</v>
       </c>
       <c r="M29">
-        <v>10.49728063363908</v>
+        <v>11.47655097967115</v>
       </c>
       <c r="N29">
-        <v>16.54271936636092</v>
+        <v>15.56344902032886</v>
       </c>
       <c r="O29">
-        <v>3.970252647926621</v>
+        <v>3.735227764878926</v>
       </c>
       <c r="P29">
-        <v>12.5724667184343</v>
+        <v>11.82822125544993</v>
       </c>
       <c r="Q29">
-        <v>12.8124667184343</v>
+        <v>12.06822125544993</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1269857429647009</v>
+        <v>0.1279020823789256</v>
       </c>
       <c r="T29">
-        <v>1.117552310627292</v>
+        <v>1.130166067578817</v>
       </c>
       <c r="U29">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V29">
         <v>0.24</v>
       </c>
       <c r="W29">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.575905221905654</v>
+        <v>2.356108559783944</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1082197393128264</v>
+        <v>0.1081857262614212</v>
       </c>
       <c r="C30">
-        <v>366.0138231373861</v>
+        <v>360.8803991805387</v>
       </c>
       <c r="D30">
-        <v>502.4195088850266</v>
+        <v>502.6934308477377</v>
       </c>
       <c r="E30">
-        <v>-243.2289062082182</v>
+        <v>-237.8215602886596</v>
       </c>
       <c r="F30">
-        <v>151.4056857476404</v>
+        <v>156.813031667199</v>
       </c>
       <c r="G30">
         <v>15</v>
@@ -3735,28 +3735,28 @@
         <v>27.04</v>
       </c>
       <c r="M30">
-        <v>11.47655097967115</v>
+        <v>11.88642780037369</v>
       </c>
       <c r="N30">
-        <v>15.56344902032886</v>
+        <v>15.15357219962632</v>
       </c>
       <c r="O30">
-        <v>3.735227764878926</v>
+        <v>3.636857327910316</v>
       </c>
       <c r="P30">
-        <v>11.82822125544993</v>
+        <v>11.516714871716</v>
       </c>
       <c r="Q30">
-        <v>12.06822125544993</v>
+        <v>11.756714871716</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1279020823789256</v>
+        <v>0.1288442341710158</v>
       </c>
       <c r="T30">
-        <v>1.130166067578817</v>
+        <v>1.143135141627568</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.356108559783944</v>
+        <v>2.274863437032774</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1081857262614212</v>
+        <v>0.108151713210016</v>
       </c>
       <c r="C31">
-        <v>360.8803991805388</v>
+        <v>355.7472740742384</v>
       </c>
       <c r="D31">
-        <v>502.6934308477378</v>
+        <v>502.967651660996</v>
       </c>
       <c r="E31">
-        <v>-237.8215602886597</v>
+        <v>-232.4142143691011</v>
       </c>
       <c r="F31">
-        <v>156.813031667199</v>
+        <v>162.2203775867576</v>
       </c>
       <c r="G31">
         <v>15</v>
@@ -3817,28 +3817,28 @@
         <v>27.04</v>
       </c>
       <c r="M31">
-        <v>11.88642780037368</v>
+        <v>12.29630462107622</v>
       </c>
       <c r="N31">
-        <v>15.15357219962632</v>
+        <v>14.74369537892378</v>
       </c>
       <c r="O31">
-        <v>3.636857327910317</v>
+        <v>3.538486890941707</v>
       </c>
       <c r="P31">
-        <v>11.516714871716</v>
+        <v>11.20520848798207</v>
       </c>
       <c r="Q31">
-        <v>11.756714871716</v>
+        <v>11.44520848798207</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1288442341710158</v>
+        <v>0.1298133045857371</v>
       </c>
       <c r="T31">
-        <v>1.143135141627568</v>
+        <v>1.15647476064914</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.274863437032775</v>
+        <v>2.199034655798349</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.108151713210016</v>
+        <v>0.1081177001586108</v>
       </c>
       <c r="C32">
-        <v>355.7472740742384</v>
+        <v>350.6144483078236</v>
       </c>
       <c r="D32">
-        <v>502.967651660996</v>
+        <v>503.2421718141397</v>
       </c>
       <c r="E32">
-        <v>-232.4142143691011</v>
+        <v>-227.0068684495425</v>
       </c>
       <c r="F32">
-        <v>162.2203775867576</v>
+        <v>167.6277235063162</v>
       </c>
       <c r="G32">
         <v>15</v>
@@ -3899,28 +3899,28 @@
         <v>27.04</v>
       </c>
       <c r="M32">
-        <v>12.29630462107622</v>
+        <v>12.70618144177877</v>
       </c>
       <c r="N32">
-        <v>14.74369537892378</v>
+        <v>14.33381855822124</v>
       </c>
       <c r="O32">
-        <v>3.538486890941707</v>
+        <v>3.440116453973097</v>
       </c>
       <c r="P32">
-        <v>11.20520848798207</v>
+        <v>10.89370210424814</v>
       </c>
       <c r="Q32">
-        <v>11.44520848798207</v>
+        <v>11.13370210424814</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1298133045857371</v>
+        <v>0.1308104639979867</v>
       </c>
       <c r="T32">
-        <v>1.15647476064914</v>
+        <v>1.170201035294526</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.199034655798349</v>
+        <v>2.128098053998402</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1081177001586108</v>
+        <v>0.1080836871072056</v>
       </c>
       <c r="C33">
-        <v>350.6144483078236</v>
+        <v>345.4819223717017</v>
       </c>
       <c r="D33">
-        <v>503.2421718141397</v>
+        <v>503.5169917975765</v>
       </c>
       <c r="E33">
-        <v>-227.0068684495425</v>
+        <v>-221.5995225299839</v>
       </c>
       <c r="F33">
-        <v>167.6277235063162</v>
+        <v>173.0350694258748</v>
       </c>
       <c r="G33">
         <v>15</v>
@@ -3981,28 +3981,28 @@
         <v>27.04</v>
       </c>
       <c r="M33">
-        <v>12.70618144177877</v>
+        <v>13.11605826248131</v>
       </c>
       <c r="N33">
-        <v>14.33381855822124</v>
+        <v>13.9239417375187</v>
       </c>
       <c r="O33">
-        <v>3.440116453973097</v>
+        <v>3.341746017004487</v>
       </c>
       <c r="P33">
-        <v>10.89370210424814</v>
+        <v>10.58219572051421</v>
       </c>
       <c r="Q33">
-        <v>11.13370210424814</v>
+        <v>10.82219572051421</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1308104639979867</v>
+        <v>0.1318369516282435</v>
       </c>
       <c r="T33">
-        <v>1.170201035294526</v>
+        <v>1.18433102390007</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.128098053998402</v>
+        <v>2.061594989810952</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1080836871072056</v>
+        <v>0.1116110340558003</v>
       </c>
       <c r="C34">
-        <v>345.4819223717017</v>
+        <v>313.0870180576514</v>
       </c>
       <c r="D34">
-        <v>503.5169917975765</v>
+        <v>476.5294334030847</v>
       </c>
       <c r="E34">
-        <v>-221.5995225299839</v>
+        <v>-216.1921766104253</v>
       </c>
       <c r="F34">
-        <v>173.0350694258748</v>
+        <v>178.4424153454333</v>
       </c>
       <c r="G34">
         <v>15</v>
@@ -4063,45 +4063,45 @@
         <v>27.04</v>
       </c>
       <c r="M34">
-        <v>13.11605826248131</v>
+        <v>16.059817381089</v>
       </c>
       <c r="N34">
-        <v>13.9239417375187</v>
+        <v>10.980182618911</v>
       </c>
       <c r="O34">
-        <v>3.341746017004487</v>
+        <v>2.63524382853864</v>
       </c>
       <c r="P34">
-        <v>10.58219572051421</v>
+        <v>8.34493879037236</v>
       </c>
       <c r="Q34">
-        <v>10.82219572051421</v>
+        <v>8.584938790372359</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1318369516282435</v>
+        <v>0.132894080680299</v>
       </c>
       <c r="T34">
-        <v>1.18433102390007</v>
+        <v>1.198882803210257</v>
       </c>
       <c r="U34">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V34">
         <v>0.24</v>
       </c>
       <c r="W34">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.061594989810952</v>
+        <v>1.683705322318332</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1116110340558003</v>
+        <v>0.1116849410043951</v>
       </c>
       <c r="C35">
-        <v>313.0870180576514</v>
+        <v>307.1451215139056</v>
       </c>
       <c r="D35">
-        <v>476.5294334030847</v>
+        <v>475.9948827788975</v>
       </c>
       <c r="E35">
-        <v>-216.1921766104253</v>
+        <v>-210.7848306908667</v>
       </c>
       <c r="F35">
-        <v>178.4424153454333</v>
+        <v>183.8497612649919</v>
       </c>
       <c r="G35">
         <v>15</v>
@@ -4145,28 +4145,28 @@
         <v>27.04</v>
       </c>
       <c r="M35">
-        <v>16.059817381089</v>
+        <v>16.54647851384927</v>
       </c>
       <c r="N35">
-        <v>10.980182618911</v>
+        <v>10.49352148615073</v>
       </c>
       <c r="O35">
-        <v>2.63524382853864</v>
+        <v>2.518445156676175</v>
       </c>
       <c r="P35">
-        <v>8.34493879037236</v>
+        <v>7.975076329474555</v>
       </c>
       <c r="Q35">
-        <v>8.584938790372359</v>
+        <v>8.215076329474554</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.132894080680299</v>
+        <v>0.1339832439460533</v>
       </c>
       <c r="T35">
-        <v>1.198882803210257</v>
+        <v>1.213875545529844</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.683705322318332</v>
+        <v>1.634184577544263</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1116849410043951</v>
+        <v>0.1117588479529899</v>
       </c>
       <c r="C36">
-        <v>307.1451215139056</v>
+        <v>301.2044228990725</v>
       </c>
       <c r="D36">
-        <v>475.9948827788975</v>
+        <v>475.4615300836231</v>
       </c>
       <c r="E36">
-        <v>-210.7848306908667</v>
+        <v>-205.3774847713081</v>
       </c>
       <c r="F36">
-        <v>183.8497612649919</v>
+        <v>189.2571071845505</v>
       </c>
       <c r="G36">
         <v>15</v>
@@ -4227,28 +4227,28 @@
         <v>27.04</v>
       </c>
       <c r="M36">
-        <v>16.54647851384927</v>
+        <v>17.03313964660955</v>
       </c>
       <c r="N36">
-        <v>10.49352148615073</v>
+        <v>10.00686035339045</v>
       </c>
       <c r="O36">
-        <v>2.518445156676175</v>
+        <v>2.401646484813709</v>
       </c>
       <c r="P36">
-        <v>7.975076329474555</v>
+        <v>7.605213868576746</v>
       </c>
       <c r="Q36">
-        <v>8.215076329474554</v>
+        <v>7.845213868576745</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1339832439460533</v>
+        <v>0.1351059199276768</v>
       </c>
       <c r="T36">
-        <v>1.213875545529844</v>
+        <v>1.229329602997727</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.634184577544263</v>
+        <v>1.587493589614427</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1117588479529899</v>
+        <v>0.1118327549015847</v>
       </c>
       <c r="C37">
-        <v>301.2044228990725</v>
+        <v>295.2649181908179</v>
       </c>
       <c r="D37">
-        <v>475.4615300836231</v>
+        <v>474.929371294927</v>
       </c>
       <c r="E37">
-        <v>-205.3774847713081</v>
+        <v>-199.9701388517495</v>
       </c>
       <c r="F37">
-        <v>189.2571071845505</v>
+        <v>194.6644531041091</v>
       </c>
       <c r="G37">
         <v>15</v>
@@ -4309,28 +4309,28 @@
         <v>27.04</v>
       </c>
       <c r="M37">
-        <v>17.03313964660955</v>
+        <v>17.51980077936982</v>
       </c>
       <c r="N37">
-        <v>10.00686035339045</v>
+        <v>9.520199220630182</v>
       </c>
       <c r="O37">
-        <v>2.401646484813709</v>
+        <v>2.284847812951244</v>
       </c>
       <c r="P37">
-        <v>7.605213868576746</v>
+        <v>7.235351407678939</v>
       </c>
       <c r="Q37">
-        <v>7.845213868576745</v>
+        <v>7.475351407678938</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1351059199276768</v>
+        <v>0.1362636795337261</v>
       </c>
       <c r="T37">
-        <v>1.229329602997727</v>
+        <v>1.24526659976148</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.587493589614427</v>
+        <v>1.543396545458471</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1118327549015847</v>
+        <v>0.1119066618501795</v>
       </c>
       <c r="C38">
-        <v>295.2649181908179</v>
+        <v>289.3266033847954</v>
       </c>
       <c r="D38">
-        <v>474.929371294927</v>
+        <v>474.398402408463</v>
       </c>
       <c r="E38">
-        <v>-199.9701388517495</v>
+        <v>-194.5627929321909</v>
       </c>
       <c r="F38">
-        <v>194.6644531041091</v>
+        <v>200.0717990236677</v>
       </c>
       <c r="G38">
         <v>15</v>
@@ -4391,28 +4391,28 @@
         <v>27.04</v>
       </c>
       <c r="M38">
-        <v>17.51980077936982</v>
+        <v>18.00646191213009</v>
       </c>
       <c r="N38">
-        <v>9.520199220630186</v>
+        <v>9.033538087869911</v>
       </c>
       <c r="O38">
-        <v>2.284847812951245</v>
+        <v>2.168049141088778</v>
       </c>
       <c r="P38">
-        <v>7.235351407678941</v>
+        <v>6.865488946781133</v>
       </c>
       <c r="Q38">
-        <v>7.47535140767894</v>
+        <v>7.105488946781132</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1362636795337261</v>
+        <v>0.1374581934129833</v>
       </c>
       <c r="T38">
-        <v>1.24526659976148</v>
+        <v>1.261709532930431</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.543396545458471</v>
+        <v>1.501683125310945</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1119066618501795</v>
+        <v>0.1303697455579324</v>
       </c>
       <c r="C39">
-        <v>289.3266033847954</v>
+        <v>180.3496255985822</v>
       </c>
       <c r="D39">
-        <v>474.398402408463</v>
+        <v>370.8287705418084</v>
       </c>
       <c r="E39">
-        <v>-194.5627929321909</v>
+        <v>-189.1554470126324</v>
       </c>
       <c r="F39">
-        <v>200.0717990236677</v>
+        <v>205.4791449432263</v>
       </c>
       <c r="G39">
         <v>15</v>
@@ -4473,45 +4473,45 @@
         <v>27.04</v>
       </c>
       <c r="M39">
-        <v>18.00646191213009</v>
+        <v>30.16433847766562</v>
       </c>
       <c r="N39">
-        <v>9.033538087869911</v>
+        <v>-3.124338477665614</v>
       </c>
       <c r="O39">
-        <v>2.168049141088778</v>
+        <v>-0.7498412346397473</v>
       </c>
       <c r="P39">
-        <v>6.865488946781133</v>
+        <v>-2.374497243025866</v>
       </c>
       <c r="Q39">
-        <v>7.105488946781132</v>
+        <v>-2.134497243025867</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1374581934129833</v>
+        <v>0.1396567695087379</v>
       </c>
       <c r="T39">
-        <v>1.261709532930431</v>
+        <v>1.29197376044349</v>
       </c>
       <c r="U39">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.24</v>
+        <v>0.2151414659666762</v>
       </c>
       <c r="W39">
-        <v>0.0684</v>
+        <v>0.1152172327960919</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y39">
-        <v>1.501683125310945</v>
+        <v>0.8964227748611511</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1303697455579324</v>
+        <v>0.1313797455579324</v>
       </c>
       <c r="C40">
-        <v>180.3496255985822</v>
+        <v>170.5658112073606</v>
       </c>
       <c r="D40">
-        <v>370.8287705418084</v>
+        <v>366.4523020701455</v>
       </c>
       <c r="E40">
-        <v>-189.1554470126324</v>
+        <v>-183.7481010930738</v>
       </c>
       <c r="F40">
-        <v>205.4791449432263</v>
+        <v>210.8864908627849</v>
       </c>
       <c r="G40">
         <v>15</v>
@@ -4555,37 +4555,37 @@
         <v>27.04</v>
       </c>
       <c r="M40">
-        <v>30.16433847766562</v>
+        <v>30.95813685865682</v>
       </c>
       <c r="N40">
-        <v>-3.124338477665614</v>
+        <v>-3.918136858656815</v>
       </c>
       <c r="O40">
-        <v>-0.7498412346397473</v>
+        <v>-0.9403528460776357</v>
       </c>
       <c r="P40">
-        <v>-2.374497243025866</v>
+        <v>-2.97778401257918</v>
       </c>
       <c r="Q40">
-        <v>-2.134497243025867</v>
+        <v>-2.73778401257918</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1396567695087379</v>
+        <v>0.1411954050744549</v>
       </c>
       <c r="T40">
-        <v>1.29197376044349</v>
+        <v>1.313153658155679</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.2151414659666762</v>
+        <v>0.2096250181213769</v>
       </c>
       <c r="W40">
-        <v>0.1152172327960919</v>
+        <v>0.1160270473397819</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8964227748611511</v>
+        <v>0.873437575505737</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1313797455579324</v>
+        <v>0.1323897455579324</v>
       </c>
       <c r="C41">
-        <v>170.5658112073606</v>
+        <v>160.8840928121002</v>
       </c>
       <c r="D41">
-        <v>366.4523020701455</v>
+        <v>362.1779295944437</v>
       </c>
       <c r="E41">
-        <v>-183.7481010930738</v>
+        <v>-178.3407551735152</v>
       </c>
       <c r="F41">
-        <v>210.8864908627849</v>
+        <v>216.2938367823434</v>
       </c>
       <c r="G41">
         <v>15</v>
@@ -4637,37 +4637,37 @@
         <v>27.04</v>
       </c>
       <c r="M41">
-        <v>30.95813685865682</v>
+        <v>31.75193523964802</v>
       </c>
       <c r="N41">
-        <v>-3.918136858656815</v>
+        <v>-4.711935239648017</v>
       </c>
       <c r="O41">
-        <v>-0.9403528460776357</v>
+        <v>-1.130864457515524</v>
       </c>
       <c r="P41">
-        <v>-2.97778401257918</v>
+        <v>-3.581070782132493</v>
       </c>
       <c r="Q41">
-        <v>-2.73778401257918</v>
+        <v>-3.341070782132494</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1411954050744549</v>
+        <v>0.1427853284923625</v>
       </c>
       <c r="T41">
-        <v>1.313153658155679</v>
+        <v>1.335039552458273</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2096250181213769</v>
+        <v>0.2043843926683424</v>
       </c>
       <c r="W41">
-        <v>0.1160270473397819</v>
+        <v>0.1167963711562873</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.873437575505737</v>
+        <v>0.8516016361180935</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1323897455579324</v>
+        <v>0.1333997455579324</v>
       </c>
       <c r="C42">
-        <v>160.8840928121002</v>
+        <v>151.3009389999438</v>
       </c>
       <c r="D42">
-        <v>362.1779295944437</v>
+        <v>358.0021217018459</v>
       </c>
       <c r="E42">
-        <v>-178.3407551735152</v>
+        <v>-172.9334092539566</v>
       </c>
       <c r="F42">
-        <v>216.2938367823434</v>
+        <v>221.701182701902</v>
       </c>
       <c r="G42">
         <v>15</v>
@@ -4719,37 +4719,37 @@
         <v>27.04</v>
       </c>
       <c r="M42">
-        <v>31.75193523964802</v>
+        <v>32.54573362063923</v>
       </c>
       <c r="N42">
-        <v>-4.711935239648017</v>
+        <v>-5.505733620639223</v>
       </c>
       <c r="O42">
-        <v>-1.130864457515524</v>
+        <v>-1.321376068953414</v>
       </c>
       <c r="P42">
-        <v>-3.581070782132493</v>
+        <v>-4.184357551685809</v>
       </c>
       <c r="Q42">
-        <v>-3.341070782132494</v>
+        <v>-3.94435755168581</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1427853284923625</v>
+        <v>0.1444291476193517</v>
       </c>
       <c r="T42">
-        <v>1.335039552458273</v>
+        <v>1.35766734148299</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2043843926683424</v>
+        <v>0.1993994074813097</v>
       </c>
       <c r="W42">
-        <v>0.1167963711562873</v>
+        <v>0.1175281669817437</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.8516016361180935</v>
+        <v>0.830830864505457</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1333997455579324</v>
+        <v>0.1344097455579324</v>
       </c>
       <c r="C43">
-        <v>151.3009389999438</v>
+        <v>141.8129793663724</v>
       </c>
       <c r="D43">
-        <v>358.0021217018459</v>
+        <v>353.9215079878331</v>
       </c>
       <c r="E43">
-        <v>-172.9334092539566</v>
+        <v>-167.526063334398</v>
       </c>
       <c r="F43">
-        <v>221.701182701902</v>
+        <v>227.1085286214606</v>
       </c>
       <c r="G43">
         <v>15</v>
@@ -4801,37 +4801,37 @@
         <v>27.04</v>
       </c>
       <c r="M43">
-        <v>32.54573362063923</v>
+        <v>33.33953200163042</v>
       </c>
       <c r="N43">
-        <v>-5.505733620639223</v>
+        <v>-6.299532001630421</v>
       </c>
       <c r="O43">
-        <v>-1.321376068953414</v>
+        <v>-1.511887680391301</v>
       </c>
       <c r="P43">
-        <v>-4.184357551685809</v>
+        <v>-4.78764432123912</v>
       </c>
       <c r="Q43">
-        <v>-3.94435755168581</v>
+        <v>-4.547644321239121</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1444291476193517</v>
+        <v>0.1461296501645129</v>
       </c>
       <c r="T43">
-        <v>1.35766734148299</v>
+        <v>1.381075399094766</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.1993994074813097</v>
+        <v>0.1946518025412785</v>
       </c>
       <c r="W43">
-        <v>0.1175281669817437</v>
+        <v>0.1182251153869403</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.830830864505457</v>
+        <v>0.811049177255327</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1344097455579324</v>
+        <v>0.1600330175373386</v>
       </c>
       <c r="C44">
-        <v>141.8129793663726</v>
+        <v>57.01854157060026</v>
       </c>
       <c r="D44">
-        <v>353.9215079878332</v>
+        <v>274.5344161116195</v>
       </c>
       <c r="E44">
-        <v>-167.526063334398</v>
+        <v>-162.1187174148394</v>
       </c>
       <c r="F44">
-        <v>227.1085286214606</v>
+        <v>232.5158745410192</v>
       </c>
       <c r="G44">
         <v>15</v>
@@ -4883,45 +4883,45 @@
         <v>27.04</v>
       </c>
       <c r="M44">
-        <v>33.33953200163042</v>
+        <v>46.68918760783666</v>
       </c>
       <c r="N44">
-        <v>-6.299532001630414</v>
+        <v>-19.64918760783666</v>
       </c>
       <c r="O44">
-        <v>-1.511887680391299</v>
+        <v>-4.715805025880797</v>
       </c>
       <c r="P44">
-        <v>-4.787644321239115</v>
+        <v>-14.93338258195586</v>
       </c>
       <c r="Q44">
-        <v>-4.547644321239115</v>
+        <v>-14.69338258195586</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1461296501645129</v>
+        <v>0.1503341562716205</v>
       </c>
       <c r="T44">
-        <v>1.381075399094765</v>
+        <v>1.43895200825615</v>
       </c>
       <c r="U44">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1946518025412785</v>
+        <v>0.1389957789479879</v>
       </c>
       <c r="W44">
-        <v>0.1182251153869403</v>
+        <v>0.172889647587244</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.8110491772553272</v>
+        <v>0.5791490789499496</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1600330175373386</v>
+        <v>0.1615830175373386</v>
       </c>
       <c r="C45">
-        <v>57.01854157060026</v>
+        <v>47.93597320457371</v>
       </c>
       <c r="D45">
-        <v>274.5344161116195</v>
+        <v>270.8591936651515</v>
       </c>
       <c r="E45">
-        <v>-162.1187174148394</v>
+        <v>-156.7113714952808</v>
       </c>
       <c r="F45">
-        <v>232.5158745410192</v>
+        <v>237.9232204605778</v>
       </c>
       <c r="G45">
         <v>15</v>
@@ -4965,37 +4965,37 @@
         <v>27.04</v>
       </c>
       <c r="M45">
-        <v>46.68918760783666</v>
+        <v>47.77498266848402</v>
       </c>
       <c r="N45">
-        <v>-19.64918760783666</v>
+        <v>-20.73498266848402</v>
       </c>
       <c r="O45">
-        <v>-4.715805025880797</v>
+        <v>-4.976395840436164</v>
       </c>
       <c r="P45">
-        <v>-14.93338258195586</v>
+        <v>-15.75858682804785</v>
       </c>
       <c r="Q45">
-        <v>-14.69338258195586</v>
+        <v>-15.51858682804786</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1503341562716205</v>
+        <v>0.1522008376336138</v>
       </c>
       <c r="T45">
-        <v>1.43895200825615</v>
+        <v>1.464647579832153</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1389957789479879</v>
+        <v>0.1358367839718973</v>
       </c>
       <c r="W45">
-        <v>0.172889647587244</v>
+        <v>0.173523973778443</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5791490789499496</v>
+        <v>0.5659865998829053</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1615830175373386</v>
+        <v>0.1631330175373387</v>
       </c>
       <c r="C46">
-        <v>47.93597320457371</v>
+        <v>38.95050614748121</v>
       </c>
       <c r="D46">
-        <v>270.8591936651515</v>
+        <v>267.2810725276176</v>
       </c>
       <c r="E46">
-        <v>-156.7113714952808</v>
+        <v>-151.3040255757222</v>
       </c>
       <c r="F46">
-        <v>237.9232204605778</v>
+        <v>243.3305663801364</v>
       </c>
       <c r="G46">
         <v>15</v>
@@ -5047,37 +5047,37 @@
         <v>27.04</v>
       </c>
       <c r="M46">
-        <v>47.77498266848402</v>
+        <v>48.86077772913139</v>
       </c>
       <c r="N46">
-        <v>-20.73498266848402</v>
+        <v>-21.82077772913138</v>
       </c>
       <c r="O46">
-        <v>-4.976395840436164</v>
+        <v>-5.236986654991532</v>
       </c>
       <c r="P46">
-        <v>-15.75858682804785</v>
+        <v>-16.58379107413985</v>
       </c>
       <c r="Q46">
-        <v>-15.51858682804786</v>
+        <v>-16.34379107413985</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1522008376336138</v>
+        <v>0.1541353983178613</v>
       </c>
       <c r="T46">
-        <v>1.464647579832153</v>
+        <v>1.491277535829101</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1358367839718973</v>
+        <v>0.1328181887725218</v>
       </c>
       <c r="W46">
-        <v>0.173523973778443</v>
+        <v>0.1741301076944776</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5659865998829053</v>
+        <v>0.5534091198855075</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1631330175373387</v>
+        <v>0.1646830175373386</v>
       </c>
       <c r="C47">
-        <v>38.95050614748121</v>
+        <v>30.05834237084156</v>
       </c>
       <c r="D47">
-        <v>267.2810725276176</v>
+        <v>263.7962546705365</v>
       </c>
       <c r="E47">
-        <v>-151.3040255757222</v>
+        <v>-145.8966796561637</v>
       </c>
       <c r="F47">
-        <v>243.3305663801364</v>
+        <v>248.737912299695</v>
       </c>
       <c r="G47">
         <v>15</v>
@@ -5129,37 +5129,37 @@
         <v>27.04</v>
       </c>
       <c r="M47">
-        <v>48.86077772913139</v>
+        <v>49.94657278977876</v>
       </c>
       <c r="N47">
-        <v>-21.82077772913138</v>
+        <v>-22.90657278977875</v>
       </c>
       <c r="O47">
-        <v>-5.236986654991532</v>
+        <v>-5.497577469546901</v>
       </c>
       <c r="P47">
-        <v>-16.58379107413985</v>
+        <v>-17.40899532023185</v>
       </c>
       <c r="Q47">
-        <v>-16.34379107413985</v>
+        <v>-17.16899532023185</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1541353983178613</v>
+        <v>0.1561416093978217</v>
       </c>
       <c r="T47">
-        <v>1.491277535829101</v>
+        <v>1.518893786492603</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1328181887725218</v>
+        <v>0.1299308368426843</v>
       </c>
       <c r="W47">
-        <v>0.1741301076944776</v>
+        <v>0.174709887961989</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5534091198855075</v>
+        <v>0.5413784868445181</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1646830175373386</v>
+        <v>0.1662330175373386</v>
       </c>
       <c r="C48">
-        <v>30.05834237084156</v>
+        <v>21.25587937209366</v>
       </c>
       <c r="D48">
-        <v>263.7962546705365</v>
+        <v>260.4011375913472</v>
       </c>
       <c r="E48">
-        <v>-145.8966796561637</v>
+        <v>-140.4893337366051</v>
       </c>
       <c r="F48">
-        <v>248.737912299695</v>
+        <v>254.1452582192535</v>
       </c>
       <c r="G48">
         <v>15</v>
@@ -5211,37 +5211,37 @@
         <v>27.04</v>
       </c>
       <c r="M48">
-        <v>49.94657278977876</v>
+        <v>51.03236785042611</v>
       </c>
       <c r="N48">
-        <v>-22.90657278977875</v>
+        <v>-23.99236785042611</v>
       </c>
       <c r="O48">
-        <v>-5.497577469546901</v>
+        <v>-5.758168284102267</v>
       </c>
       <c r="P48">
-        <v>-17.40899532023185</v>
+        <v>-18.23419956632384</v>
       </c>
       <c r="Q48">
-        <v>-17.16899532023185</v>
+        <v>-17.99419956632385</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1561416093978217</v>
+        <v>0.1582235265562711</v>
       </c>
       <c r="T48">
-        <v>1.518893786492603</v>
+        <v>1.547552159822652</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1299308368426843</v>
+        <v>0.1271663509524145</v>
       </c>
       <c r="W48">
-        <v>0.174709887961989</v>
+        <v>0.1752649967287552</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5413784868445181</v>
+        <v>0.5298597956350604</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1662330175373386</v>
+        <v>0.1677830175373387</v>
       </c>
       <c r="C49">
-        <v>21.25587937209366</v>
+        <v>12.53969775216348</v>
       </c>
       <c r="D49">
-        <v>260.4011375913472</v>
+        <v>257.0923018909756</v>
       </c>
       <c r="E49">
-        <v>-140.4893337366051</v>
+        <v>-135.0819878170465</v>
       </c>
       <c r="F49">
-        <v>254.1452582192535</v>
+        <v>259.5526041388122</v>
       </c>
       <c r="G49">
         <v>15</v>
@@ -5293,37 +5293,37 @@
         <v>27.04</v>
       </c>
       <c r="M49">
-        <v>51.03236785042611</v>
+        <v>52.11816291107348</v>
       </c>
       <c r="N49">
-        <v>-23.99236785042611</v>
+        <v>-25.07816291107348</v>
       </c>
       <c r="O49">
-        <v>-5.758168284102267</v>
+        <v>-6.018759098657635</v>
       </c>
       <c r="P49">
-        <v>-18.23419956632384</v>
+        <v>-19.05940381241584</v>
       </c>
       <c r="Q49">
-        <v>-17.99419956632385</v>
+        <v>-18.81940381241585</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1582235265562711</v>
+        <v>0.1603855174515841</v>
       </c>
       <c r="T49">
-        <v>1.547552159822652</v>
+        <v>1.577312778280781</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1271663509524145</v>
+        <v>0.1245170519742392</v>
       </c>
       <c r="W49">
-        <v>0.1752649967287552</v>
+        <v>0.1757969759635728</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5298597956350604</v>
+        <v>0.5188210498926631</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1677830175373387</v>
+        <v>0.1693330175373386</v>
       </c>
       <c r="C50">
-        <v>12.53969775216353</v>
+        <v>3.906549728235973</v>
       </c>
       <c r="D50">
-        <v>257.0923018909756</v>
+        <v>253.8664997866067</v>
       </c>
       <c r="E50">
-        <v>-135.0819878170465</v>
+        <v>-129.6746418974879</v>
       </c>
       <c r="F50">
-        <v>259.5526041388121</v>
+        <v>264.9599500583707</v>
       </c>
       <c r="G50">
         <v>15</v>
@@ -5375,37 +5375,37 @@
         <v>27.04</v>
       </c>
       <c r="M50">
-        <v>52.11816291107348</v>
+        <v>53.20395797172085</v>
       </c>
       <c r="N50">
-        <v>-25.07816291107347</v>
+        <v>-26.16395797172084</v>
       </c>
       <c r="O50">
-        <v>-6.018759098657633</v>
+        <v>-6.279349913213002</v>
       </c>
       <c r="P50">
-        <v>-19.05940381241584</v>
+        <v>-19.88460805850784</v>
       </c>
       <c r="Q50">
-        <v>-18.81940381241584</v>
+        <v>-19.64460805850785</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.160385517451584</v>
+        <v>0.1626322923035758</v>
       </c>
       <c r="T50">
-        <v>1.57731277828078</v>
+        <v>1.608240479815697</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1245170519742392</v>
+        <v>0.1219758876482343</v>
       </c>
       <c r="W50">
-        <v>0.1757969759635728</v>
+        <v>0.1763072417602345</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5188210498926633</v>
+        <v>0.5082328652009762</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1693330175373386</v>
+        <v>0.1889452196098883</v>
       </c>
       <c r="C51">
-        <v>3.906549728235973</v>
+        <v>-36.28282458762325</v>
       </c>
       <c r="D51">
-        <v>253.8664997866067</v>
+        <v>219.084471390306</v>
       </c>
       <c r="E51">
-        <v>-129.6746418974879</v>
+        <v>-124.2672959779293</v>
       </c>
       <c r="F51">
-        <v>264.9599500583707</v>
+        <v>270.3672959779293</v>
       </c>
       <c r="G51">
         <v>15</v>
@@ -5457,45 +5457,45 @@
         <v>27.04</v>
       </c>
       <c r="M51">
-        <v>53.20395797172085</v>
+        <v>63.75260839159573</v>
       </c>
       <c r="N51">
-        <v>-26.16395797172084</v>
+        <v>-36.71260839159572</v>
       </c>
       <c r="O51">
-        <v>-6.279349913213002</v>
+        <v>-8.811026013982973</v>
       </c>
       <c r="P51">
-        <v>-19.88460805850784</v>
+        <v>-27.90158237761275</v>
       </c>
       <c r="Q51">
-        <v>-19.64460805850785</v>
+        <v>-27.66158237761275</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1626322923035758</v>
+        <v>0.1660933422947467</v>
       </c>
       <c r="T51">
-        <v>1.608240479815697</v>
+        <v>1.655883135700626</v>
       </c>
       <c r="U51">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1219758876482343</v>
+        <v>0.1017934820821465</v>
       </c>
       <c r="W51">
-        <v>0.1763072417602345</v>
+        <v>0.2117970969250299</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.5082328652009762</v>
+        <v>0.4241395086756103</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1889452196098883</v>
+        <v>0.1908452196098883</v>
       </c>
       <c r="C52">
-        <v>-36.28282458762325</v>
+        <v>-44.56003755113645</v>
       </c>
       <c r="D52">
-        <v>219.084471390306</v>
+        <v>216.2146043463514</v>
       </c>
       <c r="E52">
-        <v>-124.2672959779293</v>
+        <v>-118.8599500583708</v>
       </c>
       <c r="F52">
-        <v>270.3672959779293</v>
+        <v>275.7746418974879</v>
       </c>
       <c r="G52">
         <v>15</v>
@@ -5539,37 +5539,37 @@
         <v>27.04</v>
       </c>
       <c r="M52">
-        <v>63.75260839159573</v>
+        <v>65.02766055942764</v>
       </c>
       <c r="N52">
-        <v>-36.71260839159572</v>
+        <v>-37.98766055942764</v>
       </c>
       <c r="O52">
-        <v>-8.811026013982973</v>
+        <v>-9.117038534262633</v>
       </c>
       <c r="P52">
-        <v>-27.90158237761275</v>
+        <v>-28.87062202516501</v>
       </c>
       <c r="Q52">
-        <v>-27.66158237761275</v>
+        <v>-28.63062202516501</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1660933422947467</v>
+        <v>0.1685483084640272</v>
       </c>
       <c r="T52">
-        <v>1.655883135700626</v>
+        <v>1.689676669082272</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1017934820821465</v>
+        <v>0.09979753145308477</v>
       </c>
       <c r="W52">
-        <v>0.2117970969250299</v>
+        <v>0.2122677420833626</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4241395086756103</v>
+        <v>0.4158230477211866</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1908452196098883</v>
+        <v>0.1927452196098883</v>
       </c>
       <c r="C53">
-        <v>-44.56003755113645</v>
+        <v>-52.76303581888774</v>
       </c>
       <c r="D53">
-        <v>216.2146043463514</v>
+        <v>213.4189519981587</v>
       </c>
       <c r="E53">
-        <v>-118.8599500583708</v>
+        <v>-113.4526041388121</v>
       </c>
       <c r="F53">
-        <v>275.7746418974879</v>
+        <v>281.1819878170465</v>
       </c>
       <c r="G53">
         <v>15</v>
@@ -5621,37 +5621,37 @@
         <v>27.04</v>
       </c>
       <c r="M53">
-        <v>65.02766055942764</v>
+        <v>66.30271272725956</v>
       </c>
       <c r="N53">
-        <v>-37.98766055942764</v>
+        <v>-39.26271272725955</v>
       </c>
       <c r="O53">
-        <v>-9.117038534262633</v>
+        <v>-9.423051054542293</v>
       </c>
       <c r="P53">
-        <v>-28.87062202516501</v>
+        <v>-29.83966167271726</v>
       </c>
       <c r="Q53">
-        <v>-28.63062202516501</v>
+        <v>-29.59966167271726</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1685483084640272</v>
+        <v>0.1711055648903611</v>
       </c>
       <c r="T53">
-        <v>1.689676669082272</v>
+        <v>1.724878266354819</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.09979753145308477</v>
+        <v>0.09787834815591005</v>
       </c>
       <c r="W53">
-        <v>0.2122677420833626</v>
+        <v>0.2127202855048364</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4158230477211866</v>
+        <v>0.4078264506496253</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1927452196098883</v>
+        <v>0.1946452196098883</v>
       </c>
       <c r="C54">
-        <v>-52.76303581888774</v>
+        <v>-60.89466142884734</v>
       </c>
       <c r="D54">
-        <v>213.4189519981587</v>
+        <v>210.6946723077577</v>
       </c>
       <c r="E54">
-        <v>-113.4526041388121</v>
+        <v>-108.0452582192536</v>
       </c>
       <c r="F54">
-        <v>281.1819878170465</v>
+        <v>286.5893337366051</v>
       </c>
       <c r="G54">
         <v>15</v>
@@ -5703,37 +5703,37 @@
         <v>27.04</v>
       </c>
       <c r="M54">
-        <v>66.30271272725956</v>
+        <v>67.57776489509148</v>
       </c>
       <c r="N54">
-        <v>-39.26271272725955</v>
+        <v>-40.53776489509147</v>
       </c>
       <c r="O54">
-        <v>-9.423051054542293</v>
+        <v>-9.729063574821952</v>
       </c>
       <c r="P54">
-        <v>-29.83966167271726</v>
+        <v>-30.80870132026952</v>
       </c>
       <c r="Q54">
-        <v>-29.59966167271726</v>
+        <v>-30.56870132026952</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1711055648903611</v>
+        <v>0.1737716407390922</v>
       </c>
       <c r="T54">
-        <v>1.724878266354819</v>
+        <v>1.761577803936836</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.09787834815591005</v>
+        <v>0.09603158686994949</v>
       </c>
       <c r="W54">
-        <v>0.2127202855048364</v>
+        <v>0.2131557518160659</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4078264506496253</v>
+        <v>0.400131611958123</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1946452196098883</v>
+        <v>0.1965452196098883</v>
       </c>
       <c r="C55">
-        <v>-60.89466142884734</v>
+        <v>-68.95761313425263</v>
       </c>
       <c r="D55">
-        <v>210.6946723077577</v>
+        <v>208.0390665219111</v>
       </c>
       <c r="E55">
-        <v>-108.0452582192536</v>
+        <v>-102.637912299695</v>
       </c>
       <c r="F55">
-        <v>286.5893337366051</v>
+        <v>291.9966796561637</v>
       </c>
       <c r="G55">
         <v>15</v>
@@ -5785,37 +5785,37 @@
         <v>27.04</v>
       </c>
       <c r="M55">
-        <v>67.57776489509148</v>
+        <v>68.85281706292339</v>
       </c>
       <c r="N55">
-        <v>-40.53776489509147</v>
+        <v>-41.81281706292339</v>
       </c>
       <c r="O55">
-        <v>-9.729063574821952</v>
+        <v>-10.03507609510161</v>
       </c>
       <c r="P55">
-        <v>-30.80870132026952</v>
+        <v>-31.77774096782177</v>
       </c>
       <c r="Q55">
-        <v>-30.56870132026952</v>
+        <v>-31.53774096782178</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1737716407390922</v>
+        <v>0.1765536329290725</v>
       </c>
       <c r="T55">
-        <v>1.761577803936836</v>
+        <v>1.799872973587637</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.09603158686994949</v>
+        <v>0.09425322415013561</v>
       </c>
       <c r="W55">
-        <v>0.2131557518160659</v>
+        <v>0.213575089745398</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.400131611958123</v>
+        <v>0.3927217672922317</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1965452196098883</v>
+        <v>0.1984452196098883</v>
       </c>
       <c r="C56">
-        <v>-68.95761313425263</v>
+        <v>-76.95445532104983</v>
       </c>
       <c r="D56">
-        <v>208.0390665219111</v>
+        <v>205.4495702546724</v>
       </c>
       <c r="E56">
-        <v>-102.637912299695</v>
+        <v>-97.23056638013639</v>
       </c>
       <c r="F56">
-        <v>291.9966796561637</v>
+        <v>297.4040255757222</v>
       </c>
       <c r="G56">
         <v>15</v>
@@ -5867,37 +5867,37 @@
         <v>27.04</v>
       </c>
       <c r="M56">
-        <v>68.85281706292339</v>
+        <v>70.12786923075531</v>
       </c>
       <c r="N56">
-        <v>-41.81281706292339</v>
+        <v>-43.0878692307553</v>
       </c>
       <c r="O56">
-        <v>-10.03507609510161</v>
+        <v>-10.34108861538127</v>
       </c>
       <c r="P56">
-        <v>-31.77774096782177</v>
+        <v>-32.74678061537403</v>
       </c>
       <c r="Q56">
-        <v>-31.53774096782178</v>
+        <v>-32.50678061537403</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1765536329290725</v>
+        <v>0.1794592692163852</v>
       </c>
       <c r="T56">
-        <v>1.799872973587637</v>
+        <v>1.839870150778474</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.09425322415013561</v>
+        <v>0.09253952916558769</v>
       </c>
       <c r="W56">
-        <v>0.213575089745398</v>
+        <v>0.2139791790227544</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3927217672922317</v>
+        <v>0.3855813715232821</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1984452196098883</v>
+        <v>0.2003452196098883</v>
       </c>
       <c r="C57">
-        <v>-76.95445532104983</v>
+        <v>-84.88762626754377</v>
       </c>
       <c r="D57">
-        <v>205.4495702546724</v>
+        <v>202.9237452277371</v>
       </c>
       <c r="E57">
-        <v>-97.23056638013639</v>
+        <v>-91.82322046057777</v>
       </c>
       <c r="F57">
-        <v>297.4040255757222</v>
+        <v>302.8113714952809</v>
       </c>
       <c r="G57">
         <v>15</v>
@@ -5949,37 +5949,37 @@
         <v>27.04</v>
       </c>
       <c r="M57">
-        <v>70.12786923075531</v>
+        <v>71.40292139858722</v>
       </c>
       <c r="N57">
-        <v>-43.0878692307553</v>
+        <v>-44.36292139858722</v>
       </c>
       <c r="O57">
-        <v>-10.34108861538127</v>
+        <v>-10.64710113566093</v>
       </c>
       <c r="P57">
-        <v>-32.74678061537403</v>
+        <v>-33.71582026292629</v>
       </c>
       <c r="Q57">
-        <v>-32.50678061537403</v>
+        <v>-33.47582026292628</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1794592692163852</v>
+        <v>0.182496979880394</v>
       </c>
       <c r="T57">
-        <v>1.839870150778474</v>
+        <v>1.881685381477984</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.09253952916558769</v>
+        <v>0.09088703757334504</v>
       </c>
       <c r="W57">
-        <v>0.2139791790227544</v>
+        <v>0.2143688365402052</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3855813715232821</v>
+        <v>0.3786959898889378</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2003452196098883</v>
+        <v>0.2022452196098883</v>
       </c>
       <c r="C58">
-        <v>-84.88762626754377</v>
+        <v>-92.75944580217424</v>
       </c>
       <c r="D58">
-        <v>202.9237452277371</v>
+        <v>200.4592716126652</v>
       </c>
       <c r="E58">
-        <v>-91.82322046057777</v>
+        <v>-86.41587454101921</v>
       </c>
       <c r="F58">
-        <v>302.8113714952809</v>
+        <v>308.2187174148394</v>
       </c>
       <c r="G58">
         <v>15</v>
@@ -6031,37 +6031,37 @@
         <v>27.04</v>
       </c>
       <c r="M58">
-        <v>71.40292139858722</v>
+        <v>72.67797356641914</v>
       </c>
       <c r="N58">
-        <v>-44.36292139858722</v>
+        <v>-45.63797356641913</v>
       </c>
       <c r="O58">
-        <v>-10.64710113566093</v>
+        <v>-10.95311365594059</v>
       </c>
       <c r="P58">
-        <v>-33.71582026292629</v>
+        <v>-34.68485991047854</v>
       </c>
       <c r="Q58">
-        <v>-33.47582026292628</v>
+        <v>-34.44485991047854</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.182496979880394</v>
+        <v>0.1856759794124962</v>
       </c>
       <c r="T58">
-        <v>1.881685381477984</v>
+        <v>1.925445506628636</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09088703757334504</v>
+        <v>0.08929252814223373</v>
       </c>
       <c r="W58">
-        <v>0.2143688365402052</v>
+        <v>0.2147448218640613</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3786959898889378</v>
+        <v>0.3720522005926407</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2022452196098883</v>
+        <v>0.2041452196098883</v>
       </c>
       <c r="C59">
-        <v>-92.75944580217424</v>
+        <v>-100.5721224099748</v>
       </c>
       <c r="D59">
-        <v>200.4592716126652</v>
+        <v>198.0539409244233</v>
       </c>
       <c r="E59">
-        <v>-86.41587454101921</v>
+        <v>-81.00852862146058</v>
       </c>
       <c r="F59">
-        <v>308.2187174148394</v>
+        <v>313.6260633343981</v>
       </c>
       <c r="G59">
         <v>15</v>
@@ -6113,37 +6113,37 @@
         <v>27.04</v>
       </c>
       <c r="M59">
-        <v>72.67797356641914</v>
+        <v>73.95302573425107</v>
       </c>
       <c r="N59">
-        <v>-45.63797356641913</v>
+        <v>-46.91302573425106</v>
       </c>
       <c r="O59">
-        <v>-10.95311365594059</v>
+        <v>-11.25912617622025</v>
       </c>
       <c r="P59">
-        <v>-34.68485991047854</v>
+        <v>-35.65389955803081</v>
       </c>
       <c r="Q59">
-        <v>-34.44485991047854</v>
+        <v>-35.41389955803081</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1856759794124962</v>
+        <v>0.1890063598746984</v>
       </c>
       <c r="T59">
-        <v>1.925445506628636</v>
+        <v>1.97128944726265</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08929252814223373</v>
+        <v>0.08775300179495382</v>
       </c>
       <c r="W59">
-        <v>0.2147448218640613</v>
+        <v>0.2151078421767499</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3720522005926407</v>
+        <v>0.3656375074789743</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2041452196098883</v>
+        <v>0.2060452196098883</v>
       </c>
       <c r="C60">
-        <v>-100.5721224099747</v>
+        <v>-108.3277598334702</v>
       </c>
       <c r="D60">
-        <v>198.0539409244233</v>
+        <v>195.7056494204864</v>
       </c>
       <c r="E60">
-        <v>-81.0085286214607</v>
+        <v>-75.60118270190208</v>
       </c>
       <c r="F60">
-        <v>313.6260633343979</v>
+        <v>319.0334092539566</v>
       </c>
       <c r="G60">
         <v>15</v>
@@ -6195,37 +6195,37 @@
         <v>27.04</v>
       </c>
       <c r="M60">
-        <v>73.95302573425104</v>
+        <v>75.22807790208296</v>
       </c>
       <c r="N60">
-        <v>-46.91302573425104</v>
+        <v>-48.18807790208295</v>
       </c>
       <c r="O60">
-        <v>-11.25912617622025</v>
+        <v>-11.56513869649991</v>
       </c>
       <c r="P60">
-        <v>-35.65389955803079</v>
+        <v>-36.62293920558304</v>
       </c>
       <c r="Q60">
-        <v>-35.41389955803078</v>
+        <v>-36.38293920558304</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1890063598746984</v>
+        <v>0.1924991979204228</v>
       </c>
       <c r="T60">
-        <v>1.97128944726265</v>
+        <v>2.01936967768369</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08775300179495385</v>
+        <v>0.08626566278148005</v>
       </c>
       <c r="W60">
-        <v>0.2151078421767499</v>
+        <v>0.215458556716127</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3656375074789745</v>
+        <v>0.3594402615895003</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2060452196098883</v>
+        <v>0.2079452196098883</v>
       </c>
       <c r="C61">
-        <v>-108.3277598334702</v>
+        <v>-116.0283632094838</v>
       </c>
       <c r="D61">
-        <v>195.7056494204864</v>
+        <v>193.4123919640313</v>
       </c>
       <c r="E61">
-        <v>-75.60118270190208</v>
+        <v>-70.19383678234351</v>
       </c>
       <c r="F61">
-        <v>319.0334092539566</v>
+        <v>324.4407551735151</v>
       </c>
       <c r="G61">
         <v>15</v>
@@ -6277,37 +6277,37 @@
         <v>27.04</v>
       </c>
       <c r="M61">
-        <v>75.22807790208296</v>
+        <v>76.50313006991487</v>
       </c>
       <c r="N61">
-        <v>-48.18807790208295</v>
+        <v>-49.46313006991487</v>
       </c>
       <c r="O61">
-        <v>-11.56513869649991</v>
+        <v>-11.87115121677957</v>
       </c>
       <c r="P61">
-        <v>-36.62293920558304</v>
+        <v>-37.5919788531353</v>
       </c>
       <c r="Q61">
-        <v>-36.38293920558304</v>
+        <v>-37.3519788531353</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1924991979204228</v>
+        <v>0.1961666778684333</v>
       </c>
       <c r="T61">
-        <v>2.01936967768369</v>
+        <v>2.069853919625782</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08626566278148005</v>
+        <v>0.08482790173512206</v>
       </c>
       <c r="W61">
-        <v>0.215458556716127</v>
+        <v>0.2157975807708582</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3594402615895003</v>
+        <v>0.3534495905630086</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2079452196098883</v>
+        <v>0.2098452196098883</v>
       </c>
       <c r="C62">
-        <v>-116.0283632094838</v>
+        <v>-123.6758447794781</v>
       </c>
       <c r="D62">
-        <v>193.4123919640313</v>
+        <v>191.1722563135956</v>
       </c>
       <c r="E62">
-        <v>-70.19383678234351</v>
+        <v>-64.78649086278489</v>
       </c>
       <c r="F62">
-        <v>324.4407551735151</v>
+        <v>329.8481010930738</v>
       </c>
       <c r="G62">
         <v>15</v>
@@ -6359,37 +6359,37 @@
         <v>27.04</v>
       </c>
       <c r="M62">
-        <v>76.50313006991487</v>
+        <v>77.77818223774679</v>
       </c>
       <c r="N62">
-        <v>-49.46313006991487</v>
+        <v>-50.73818223774678</v>
       </c>
       <c r="O62">
-        <v>-11.87115121677957</v>
+        <v>-12.17716373705923</v>
       </c>
       <c r="P62">
-        <v>-37.5919788531353</v>
+        <v>-38.56101850068755</v>
       </c>
       <c r="Q62">
-        <v>-37.3519788531353</v>
+        <v>-38.32101850068755</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1961666778684333</v>
+        <v>0.2000222337112137</v>
       </c>
       <c r="T62">
-        <v>2.069853919625782</v>
+        <v>2.122927097052085</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08482790173512206</v>
+        <v>0.08343728039520203</v>
       </c>
       <c r="W62">
-        <v>0.2157975807708582</v>
+        <v>0.2161254892828114</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3534495905630086</v>
+        <v>0.3476553349800084</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2098452196098883</v>
+        <v>0.2117452196098882</v>
       </c>
       <c r="C63">
-        <v>-123.6758447794781</v>
+        <v>-131.2720292076103</v>
       </c>
       <c r="D63">
-        <v>191.1722563135956</v>
+        <v>188.983417805022</v>
       </c>
       <c r="E63">
-        <v>-64.78649086278489</v>
+        <v>-59.37914494322632</v>
       </c>
       <c r="F63">
-        <v>329.8481010930738</v>
+        <v>335.2554470126323</v>
       </c>
       <c r="G63">
         <v>15</v>
@@ -6441,37 +6441,37 @@
         <v>27.04</v>
       </c>
       <c r="M63">
-        <v>77.77818223774679</v>
+        <v>79.05323440557871</v>
       </c>
       <c r="N63">
-        <v>-50.73818223774678</v>
+        <v>-52.0132344055787</v>
       </c>
       <c r="O63">
-        <v>-12.17716373705923</v>
+        <v>-12.48317625733889</v>
       </c>
       <c r="P63">
-        <v>-38.56101850068755</v>
+        <v>-39.53005814823981</v>
       </c>
       <c r="Q63">
-        <v>-38.32101850068755</v>
+        <v>-39.29005814823981</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2000222337112137</v>
+        <v>0.2040807135457193</v>
       </c>
       <c r="T63">
-        <v>2.122927097052085</v>
+        <v>2.178793599606087</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08343728039520203</v>
+        <v>0.08209151780818263</v>
       </c>
       <c r="W63">
-        <v>0.2161254892828114</v>
+        <v>0.2164428201008305</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3476553349800084</v>
+        <v>0.3420479908674277</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2117452196098882</v>
+        <v>0.2136452196098883</v>
       </c>
       <c r="C64">
-        <v>-131.2720292076103</v>
+        <v>-138.8186585375878</v>
       </c>
       <c r="D64">
-        <v>188.983417805022</v>
+        <v>186.8441343946031</v>
       </c>
       <c r="E64">
-        <v>-59.37914494322632</v>
+        <v>-53.9717990236677</v>
       </c>
       <c r="F64">
-        <v>335.2554470126323</v>
+        <v>340.6627929321909</v>
       </c>
       <c r="G64">
         <v>15</v>
@@ -6523,37 +6523,37 @@
         <v>27.04</v>
       </c>
       <c r="M64">
-        <v>79.05323440557871</v>
+        <v>80.32828657341062</v>
       </c>
       <c r="N64">
-        <v>-52.0132344055787</v>
+        <v>-53.28828657341062</v>
       </c>
       <c r="O64">
-        <v>-12.48317625733889</v>
+        <v>-12.78918877761855</v>
       </c>
       <c r="P64">
-        <v>-39.53005814823981</v>
+        <v>-40.49909779579207</v>
       </c>
       <c r="Q64">
-        <v>-39.29005814823981</v>
+        <v>-40.25909779579207</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2040807135457193</v>
+        <v>0.2083585706685766</v>
       </c>
       <c r="T64">
-        <v>2.178793599606087</v>
+        <v>2.237679913108954</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08209151780818263</v>
+        <v>0.08078847784297338</v>
       </c>
       <c r="W64">
-        <v>0.2164428201008305</v>
+        <v>0.2167500769246269</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3420479908674277</v>
+        <v>0.3366186576790559</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2136452196098883</v>
+        <v>0.2155452196098883</v>
       </c>
       <c r="C65">
-        <v>-138.8186585375878</v>
+        <v>-146.3173968166226</v>
       </c>
       <c r="D65">
-        <v>186.8441343946031</v>
+        <v>184.7527420351269</v>
       </c>
       <c r="E65">
-        <v>-53.9717990236677</v>
+        <v>-48.56445310410913</v>
       </c>
       <c r="F65">
-        <v>340.6627929321909</v>
+        <v>346.0701388517495</v>
       </c>
       <c r="G65">
         <v>15</v>
@@ -6605,37 +6605,37 @@
         <v>27.04</v>
       </c>
       <c r="M65">
-        <v>80.32828657341062</v>
+        <v>81.60333874124254</v>
       </c>
       <c r="N65">
-        <v>-53.28828657341062</v>
+        <v>-54.56333874124253</v>
       </c>
       <c r="O65">
-        <v>-12.78918877761855</v>
+        <v>-13.09520129789821</v>
       </c>
       <c r="P65">
-        <v>-40.49909779579207</v>
+        <v>-41.46813744334433</v>
       </c>
       <c r="Q65">
-        <v>-40.25909779579207</v>
+        <v>-41.22813744334432</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2083585706685766</v>
+        <v>0.2128740865204815</v>
       </c>
       <c r="T65">
-        <v>2.237679913108954</v>
+        <v>2.299837688473092</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08078847784297338</v>
+        <v>0.07952615787667693</v>
       </c>
       <c r="W65">
-        <v>0.2167500769246269</v>
+        <v>0.2170477319726796</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3366186576790559</v>
+        <v>0.3313589911528205</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2155452196098883</v>
+        <v>0.2174452196098883</v>
       </c>
       <c r="C66">
-        <v>-146.3173968166226</v>
+        <v>-153.7698344122825</v>
       </c>
       <c r="D66">
-        <v>184.7527420351269</v>
+        <v>182.7076503590256</v>
       </c>
       <c r="E66">
-        <v>-48.56445310410913</v>
+        <v>-43.15710718455051</v>
       </c>
       <c r="F66">
-        <v>346.0701388517495</v>
+        <v>351.4774847713081</v>
       </c>
       <c r="G66">
         <v>15</v>
@@ -6687,37 +6687,37 @@
         <v>27.04</v>
       </c>
       <c r="M66">
-        <v>81.60333874124254</v>
+        <v>82.87839090907445</v>
       </c>
       <c r="N66">
-        <v>-54.56333874124253</v>
+        <v>-55.83839090907445</v>
       </c>
       <c r="O66">
-        <v>-13.09520129789821</v>
+        <v>-13.40121381817787</v>
       </c>
       <c r="P66">
-        <v>-41.46813744334433</v>
+        <v>-42.43717709089658</v>
       </c>
       <c r="Q66">
-        <v>-41.22813744334432</v>
+        <v>-42.19717709089658</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2128740865204815</v>
+        <v>0.2176476318496381</v>
       </c>
       <c r="T66">
-        <v>2.299837688473092</v>
+        <v>2.36554733671518</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07952615787667693</v>
+        <v>0.07830267852472805</v>
       </c>
       <c r="W66">
-        <v>0.2170477319726796</v>
+        <v>0.2173362284038691</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3313589911528205</v>
+        <v>0.3262611605197002</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2174452196098883</v>
+        <v>0.2193452196098883</v>
       </c>
       <c r="C67">
-        <v>-153.7698344122825</v>
+        <v>-161.1774920457707</v>
       </c>
       <c r="D67">
-        <v>182.7076503590256</v>
+        <v>180.707338645096</v>
       </c>
       <c r="E67">
-        <v>-43.15710718455051</v>
+        <v>-37.74976126499195</v>
       </c>
       <c r="F67">
-        <v>351.4774847713081</v>
+        <v>356.8848306908667</v>
       </c>
       <c r="G67">
         <v>15</v>
@@ -6769,37 +6769,37 @@
         <v>27.04</v>
       </c>
       <c r="M67">
-        <v>82.87839090907445</v>
+        <v>84.15344307690637</v>
       </c>
       <c r="N67">
-        <v>-55.83839090907445</v>
+        <v>-57.11344307690636</v>
       </c>
       <c r="O67">
-        <v>-13.40121381817787</v>
+        <v>-13.70722633845753</v>
       </c>
       <c r="P67">
-        <v>-42.43717709089658</v>
+        <v>-43.40621673844883</v>
       </c>
       <c r="Q67">
-        <v>-42.19717709089658</v>
+        <v>-43.16621673844883</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2176476318496381</v>
+        <v>0.2227019739628628</v>
       </c>
       <c r="T67">
-        <v>2.36554733671518</v>
+        <v>2.435122258383274</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07830267852472805</v>
+        <v>0.07711627430465641</v>
       </c>
       <c r="W67">
-        <v>0.2173362284038691</v>
+        <v>0.217615982518962</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3262611605197002</v>
+        <v>0.321317809602735</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2193452196098883</v>
+        <v>0.2212452196098883</v>
       </c>
       <c r="C68">
-        <v>-161.1774920457707</v>
+        <v>-168.5418245631353</v>
       </c>
       <c r="D68">
-        <v>180.707338645096</v>
+        <v>178.75035204729</v>
       </c>
       <c r="E68">
-        <v>-37.74976126499195</v>
+        <v>-32.34241534543332</v>
       </c>
       <c r="F68">
-        <v>356.8848306908667</v>
+        <v>362.2921766104253</v>
       </c>
       <c r="G68">
         <v>15</v>
@@ -6851,37 +6851,37 @@
         <v>27.04</v>
       </c>
       <c r="M68">
-        <v>84.15344307690637</v>
+        <v>85.42849524473829</v>
       </c>
       <c r="N68">
-        <v>-57.11344307690636</v>
+        <v>-58.38849524473828</v>
       </c>
       <c r="O68">
-        <v>-13.70722633845753</v>
+        <v>-14.01323885873719</v>
       </c>
       <c r="P68">
-        <v>-43.40621673844883</v>
+        <v>-44.37525638600109</v>
       </c>
       <c r="Q68">
-        <v>-43.16621673844883</v>
+        <v>-44.13525638600109</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2227019739628628</v>
+        <v>0.2280626398405253</v>
       </c>
       <c r="T68">
-        <v>2.435122258383274</v>
+        <v>2.508913841970646</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07711627430465641</v>
+        <v>0.07596528513593019</v>
       </c>
       <c r="W68">
-        <v>0.217615982518962</v>
+        <v>0.2178873857649477</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.321317809602735</v>
+        <v>0.3165220213997092</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2212452196098883</v>
+        <v>0.2231452196098883</v>
       </c>
       <c r="C69">
-        <v>-168.5418245631353</v>
+        <v>-175.8642244640583</v>
       </c>
       <c r="D69">
-        <v>178.75035204729</v>
+        <v>176.8352980659256</v>
       </c>
       <c r="E69">
-        <v>-32.34241534543332</v>
+        <v>-26.93506942587476</v>
       </c>
       <c r="F69">
-        <v>362.2921766104253</v>
+        <v>367.6995225299839</v>
       </c>
       <c r="G69">
         <v>15</v>
@@ -6933,37 +6933,37 @@
         <v>27.04</v>
       </c>
       <c r="M69">
-        <v>85.42849524473829</v>
+        <v>86.7035474125702</v>
       </c>
       <c r="N69">
-        <v>-58.38849524473828</v>
+        <v>-59.6635474125702</v>
       </c>
       <c r="O69">
-        <v>-14.01323885873719</v>
+        <v>-14.31925137901685</v>
       </c>
       <c r="P69">
-        <v>-44.37525638600109</v>
+        <v>-45.34429603355335</v>
       </c>
       <c r="Q69">
-        <v>-44.13525638600109</v>
+        <v>-45.10429603355335</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2280626398405253</v>
+        <v>0.2337583473355417</v>
       </c>
       <c r="T69">
-        <v>2.508913841970646</v>
+        <v>2.587317399532229</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07596528513593019</v>
+        <v>0.07484814858981358</v>
       </c>
       <c r="W69">
-        <v>0.2178873857649477</v>
+        <v>0.218150806562522</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3165220213997092</v>
+        <v>0.31186728579089</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2231452196098883</v>
+        <v>0.2250452196098883</v>
       </c>
       <c r="C70">
-        <v>-175.8642244640583</v>
+        <v>-183.146025206214</v>
       </c>
       <c r="D70">
-        <v>176.8352980659256</v>
+        <v>174.9608432433284</v>
       </c>
       <c r="E70">
-        <v>-26.93506942587476</v>
+        <v>-21.52772350631619</v>
       </c>
       <c r="F70">
-        <v>367.6995225299839</v>
+        <v>373.1068684495424</v>
       </c>
       <c r="G70">
         <v>15</v>
@@ -7015,37 +7015,37 @@
         <v>27.04</v>
       </c>
       <c r="M70">
-        <v>86.7035474125702</v>
+        <v>87.97859958040212</v>
       </c>
       <c r="N70">
-        <v>-59.6635474125702</v>
+        <v>-60.93859958040211</v>
       </c>
       <c r="O70">
-        <v>-14.31925137901685</v>
+        <v>-14.62526389929651</v>
       </c>
       <c r="P70">
-        <v>-45.34429603355335</v>
+        <v>-46.31333568110561</v>
       </c>
       <c r="Q70">
-        <v>-45.10429603355335</v>
+        <v>-46.0733356811056</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2337583473355417</v>
+        <v>0.2398215198302366</v>
       </c>
       <c r="T70">
-        <v>2.587317399532229</v>
+        <v>2.670779251130043</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07484814858981358</v>
+        <v>0.0737633928131496</v>
       </c>
       <c r="W70">
-        <v>0.218150806562522</v>
+        <v>0.2184065919746593</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.31186728579089</v>
+        <v>0.30734747005479</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2250452196098883</v>
+        <v>0.2269452196098883</v>
       </c>
       <c r="C71">
-        <v>-183.146025206214</v>
+        <v>-190.3885043016755</v>
       </c>
       <c r="D71">
-        <v>174.9608432433284</v>
+        <v>173.1257100674255</v>
       </c>
       <c r="E71">
-        <v>-21.52772350631619</v>
+        <v>-16.12037758675757</v>
       </c>
       <c r="F71">
-        <v>373.1068684495424</v>
+        <v>378.5142143691011</v>
       </c>
       <c r="G71">
         <v>15</v>
@@ -7097,37 +7097,37 @@
         <v>27.04</v>
       </c>
       <c r="M71">
-        <v>87.97859958040212</v>
+        <v>89.25365174823403</v>
       </c>
       <c r="N71">
-        <v>-60.93859958040211</v>
+        <v>-62.21365174823403</v>
       </c>
       <c r="O71">
-        <v>-14.62526389929651</v>
+        <v>-14.93127641957617</v>
       </c>
       <c r="P71">
-        <v>-46.31333568110561</v>
+        <v>-47.28237532865786</v>
       </c>
       <c r="Q71">
-        <v>-46.0733356811056</v>
+        <v>-47.04237532865786</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2398215198302366</v>
+        <v>0.2462889038245778</v>
       </c>
       <c r="T71">
-        <v>2.670779251130043</v>
+        <v>2.75980522616771</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0737633928131496</v>
+        <v>0.07270963005867603</v>
       </c>
       <c r="W71">
-        <v>0.2184065919746593</v>
+        <v>0.2186550692321642</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.30734747005479</v>
+        <v>0.3029567919111502</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2269452196098883</v>
+        <v>0.2288452196098883</v>
       </c>
       <c r="C72">
-        <v>-190.3885043016755</v>
+        <v>-197.592886220476</v>
       </c>
       <c r="D72">
-        <v>173.1257100674255</v>
+        <v>171.3286740681836</v>
       </c>
       <c r="E72">
-        <v>-16.12037758675757</v>
+        <v>-10.713031667199</v>
       </c>
       <c r="F72">
-        <v>378.5142143691011</v>
+        <v>383.9215602886596</v>
       </c>
       <c r="G72">
         <v>15</v>
@@ -7179,37 +7179,37 @@
         <v>27.04</v>
       </c>
       <c r="M72">
-        <v>89.25365174823403</v>
+        <v>90.52870391606595</v>
       </c>
       <c r="N72">
-        <v>-62.21365174823403</v>
+        <v>-63.48870391606594</v>
       </c>
       <c r="O72">
-        <v>-14.93127641957617</v>
+        <v>-15.23728893985583</v>
       </c>
       <c r="P72">
-        <v>-47.28237532865786</v>
+        <v>-48.25141497621011</v>
       </c>
       <c r="Q72">
-        <v>-47.04237532865786</v>
+        <v>-48.01141497621011</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2462889038245778</v>
+        <v>0.2532023143012874</v>
       </c>
       <c r="T72">
-        <v>2.75980522616771</v>
+        <v>2.85497092362177</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07270963005867603</v>
+        <v>0.07168555076207497</v>
       </c>
       <c r="W72">
-        <v>0.2186550692321642</v>
+        <v>0.2188965471303027</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3029567919111502</v>
+        <v>0.2986897948419791</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2288452196098883</v>
+        <v>0.2307452196098883</v>
       </c>
       <c r="C73">
-        <v>-197.5928862204759</v>
+        <v>-204.7603451151966</v>
       </c>
       <c r="D73">
-        <v>171.3286740681836</v>
+        <v>169.5685610930216</v>
       </c>
       <c r="E73">
-        <v>-10.71303166719906</v>
+        <v>-5.305685747640439</v>
       </c>
       <c r="F73">
-        <v>383.9215602886596</v>
+        <v>389.3289062082182</v>
       </c>
       <c r="G73">
         <v>15</v>
@@ -7261,37 +7261,37 @@
         <v>27.04</v>
       </c>
       <c r="M73">
-        <v>90.52870391606594</v>
+        <v>91.80375608389785</v>
       </c>
       <c r="N73">
-        <v>-63.48870391606593</v>
+        <v>-64.76375608389785</v>
       </c>
       <c r="O73">
-        <v>-15.23728893985582</v>
+        <v>-15.54330146013548</v>
       </c>
       <c r="P73">
-        <v>-48.25141497621011</v>
+        <v>-49.22045462376236</v>
       </c>
       <c r="Q73">
-        <v>-48.01141497621011</v>
+        <v>-48.98045462376236</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2532023143012874</v>
+        <v>0.2606095398120476</v>
       </c>
       <c r="T73">
-        <v>2.854970923621769</v>
+        <v>2.956934170893975</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07168555076207499</v>
+        <v>0.07068991811260171</v>
       </c>
       <c r="W73">
-        <v>0.2188965471303027</v>
+        <v>0.2191313173090485</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2986897948419791</v>
+        <v>0.2945413254691739</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2307452196098883</v>
+        <v>0.2326452196098883</v>
       </c>
       <c r="C74">
-        <v>-204.7603451151966</v>
+        <v>-211.8920073793178</v>
       </c>
       <c r="D74">
-        <v>169.5685610930216</v>
+        <v>167.8442447484589</v>
       </c>
       <c r="E74">
-        <v>-5.305685747640439</v>
+        <v>0.1016601719181267</v>
       </c>
       <c r="F74">
-        <v>389.3289062082182</v>
+        <v>394.7362521277768</v>
       </c>
       <c r="G74">
         <v>15</v>
@@ -7343,37 +7343,37 @@
         <v>27.04</v>
       </c>
       <c r="M74">
-        <v>91.80375608389785</v>
+        <v>93.07880825172977</v>
       </c>
       <c r="N74">
-        <v>-64.76375608389785</v>
+        <v>-66.03880825172976</v>
       </c>
       <c r="O74">
-        <v>-15.54330146013548</v>
+        <v>-15.84931398041514</v>
       </c>
       <c r="P74">
-        <v>-49.22045462376236</v>
+        <v>-50.18949427131462</v>
       </c>
       <c r="Q74">
-        <v>-48.98045462376236</v>
+        <v>-49.94949427131462</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2606095398120476</v>
+        <v>0.2685654486939753</v>
       </c>
       <c r="T74">
-        <v>2.956934170893975</v>
+        <v>3.066450251297455</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07068991811260171</v>
+        <v>0.06972156306996334</v>
       </c>
       <c r="W74">
-        <v>0.2191313173090485</v>
+        <v>0.2193596554281027</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2945413254691739</v>
+        <v>0.290506512791514</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2326452196098883</v>
+        <v>0.2345452196098883</v>
       </c>
       <c r="C75">
-        <v>-211.8920073793178</v>
+        <v>-218.9889540510502</v>
       </c>
       <c r="D75">
-        <v>167.8442447484589</v>
+        <v>166.1546439962852</v>
       </c>
       <c r="E75">
-        <v>0.1016601719181267</v>
+        <v>5.509006091476749</v>
       </c>
       <c r="F75">
-        <v>394.7362521277768</v>
+        <v>400.1435980473354</v>
       </c>
       <c r="G75">
         <v>15</v>
@@ -7425,37 +7425,37 @@
         <v>27.04</v>
       </c>
       <c r="M75">
-        <v>93.07880825172977</v>
+        <v>94.35386041956168</v>
       </c>
       <c r="N75">
-        <v>-66.03880825172976</v>
+        <v>-67.31386041956168</v>
       </c>
       <c r="O75">
-        <v>-15.84931398041514</v>
+        <v>-16.1553265006948</v>
       </c>
       <c r="P75">
-        <v>-50.18949427131462</v>
+        <v>-51.15853391886688</v>
       </c>
       <c r="Q75">
-        <v>-49.94949427131462</v>
+        <v>-50.91853391886688</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2685654486939753</v>
+        <v>0.2771333505668205</v>
       </c>
       <c r="T75">
-        <v>3.066450251297455</v>
+        <v>3.184390645578127</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06972156306996334</v>
+        <v>0.0687793797852341</v>
       </c>
       <c r="W75">
-        <v>0.2193596554281027</v>
+        <v>0.2195818222466418</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.290506512791514</v>
+        <v>0.2865807491051421</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2345452196098883</v>
+        <v>0.2364452196098883</v>
       </c>
       <c r="C76">
-        <v>-218.9889540510502</v>
+        <v>-226.0522230734222</v>
       </c>
       <c r="D76">
-        <v>166.1546439962852</v>
+        <v>164.4987208934718</v>
       </c>
       <c r="E76">
-        <v>5.509006091476749</v>
+        <v>10.91635201103531</v>
       </c>
       <c r="F76">
-        <v>400.1435980473354</v>
+        <v>405.550943966894</v>
       </c>
       <c r="G76">
         <v>15</v>
@@ -7507,37 +7507,37 @@
         <v>27.04</v>
       </c>
       <c r="M76">
-        <v>94.35386041956168</v>
+        <v>95.6289125873936</v>
       </c>
       <c r="N76">
-        <v>-67.31386041956168</v>
+        <v>-68.58891258739359</v>
       </c>
       <c r="O76">
-        <v>-16.1553265006948</v>
+        <v>-16.46133902097446</v>
       </c>
       <c r="P76">
-        <v>-51.15853391886688</v>
+        <v>-52.12757356641913</v>
       </c>
       <c r="Q76">
-        <v>-50.91853391886688</v>
+        <v>-51.88757356641913</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2771333505668205</v>
+        <v>0.2863866845894933</v>
       </c>
       <c r="T76">
-        <v>3.184390645578127</v>
+        <v>3.311766271401252</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0687793797852341</v>
+        <v>0.06786232138809764</v>
       </c>
       <c r="W76">
-        <v>0.2195818222466418</v>
+        <v>0.2197980646166866</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2865807491051421</v>
+        <v>0.2827596724504069</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2364452196098883</v>
+        <v>0.2383452196098883</v>
       </c>
       <c r="C77">
-        <v>-226.0522230734222</v>
+        <v>-233.0828114205561</v>
       </c>
       <c r="D77">
-        <v>164.4987208934718</v>
+        <v>162.8754784658964</v>
       </c>
       <c r="E77">
-        <v>10.91635201103531</v>
+        <v>16.32369793059388</v>
       </c>
       <c r="F77">
-        <v>405.550943966894</v>
+        <v>410.9582898864525</v>
       </c>
       <c r="G77">
         <v>15</v>
@@ -7589,37 +7589,37 @@
         <v>27.04</v>
       </c>
       <c r="M77">
-        <v>95.6289125873936</v>
+        <v>96.9039647552255</v>
       </c>
       <c r="N77">
-        <v>-68.58891258739359</v>
+        <v>-69.8639647552255</v>
       </c>
       <c r="O77">
-        <v>-16.46133902097446</v>
+        <v>-16.76735154125412</v>
       </c>
       <c r="P77">
-        <v>-52.12757356641913</v>
+        <v>-53.09661321397138</v>
       </c>
       <c r="Q77">
-        <v>-51.88757356641913</v>
+        <v>-52.85661321397138</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2863866845894933</v>
+        <v>0.2964111297807223</v>
       </c>
       <c r="T77">
-        <v>3.311766271401252</v>
+        <v>3.449756532709638</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06786232138809764</v>
+        <v>0.06696939610667531</v>
       </c>
       <c r="W77">
-        <v>0.2197980646166866</v>
+        <v>0.220008616398046</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2827596724504069</v>
+        <v>0.2790391504444805</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2383452196098883</v>
+        <v>0.2402452196098883</v>
       </c>
       <c r="C78">
-        <v>-233.0828114205561</v>
+        <v>-240.0816770992843</v>
       </c>
       <c r="D78">
-        <v>162.8754784658964</v>
+        <v>161.2839587067268</v>
       </c>
       <c r="E78">
-        <v>16.32369793059388</v>
+        <v>21.7310438501525</v>
       </c>
       <c r="F78">
-        <v>410.9582898864525</v>
+        <v>416.3656358060111</v>
       </c>
       <c r="G78">
         <v>15</v>
@@ -7671,37 +7671,37 @@
         <v>27.04</v>
       </c>
       <c r="M78">
-        <v>96.9039647552255</v>
+        <v>98.17901692305743</v>
       </c>
       <c r="N78">
-        <v>-69.8639647552255</v>
+        <v>-71.13901692305743</v>
       </c>
       <c r="O78">
-        <v>-16.76735154125412</v>
+        <v>-17.07336406153378</v>
       </c>
       <c r="P78">
-        <v>-53.09661321397138</v>
+        <v>-54.06565286152365</v>
       </c>
       <c r="Q78">
-        <v>-52.85661321397138</v>
+        <v>-53.82565286152364</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2964111297807223</v>
+        <v>0.3073072658581449</v>
       </c>
       <c r="T78">
-        <v>3.449756532709638</v>
+        <v>3.599745947175274</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06696939610667531</v>
+        <v>0.0660996636897055</v>
       </c>
       <c r="W78">
-        <v>0.220008616398046</v>
+        <v>0.2202136993019674</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2790391504444805</v>
+        <v>0.2754152653737729</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2402452196098883</v>
+        <v>0.2421452196098883</v>
       </c>
       <c r="C79">
-        <v>-240.0816770992843</v>
+        <v>-247.0497410345483</v>
       </c>
       <c r="D79">
-        <v>161.2839587067268</v>
+        <v>159.7232406910214</v>
       </c>
       <c r="E79">
-        <v>21.7310438501525</v>
+        <v>27.13838976971107</v>
       </c>
       <c r="F79">
-        <v>416.3656358060111</v>
+        <v>421.7729817255697</v>
       </c>
       <c r="G79">
         <v>15</v>
@@ -7753,37 +7753,37 @@
         <v>27.04</v>
       </c>
       <c r="M79">
-        <v>98.17901692305743</v>
+        <v>99.45406909088933</v>
       </c>
       <c r="N79">
-        <v>-71.13901692305743</v>
+        <v>-72.41406909088933</v>
       </c>
       <c r="O79">
-        <v>-17.07336406153378</v>
+        <v>-17.37937658181344</v>
       </c>
       <c r="P79">
-        <v>-54.06565286152365</v>
+        <v>-55.03469250907589</v>
       </c>
       <c r="Q79">
-        <v>-53.82565286152364</v>
+        <v>-54.79469250907589</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3073072658581449</v>
+        <v>0.3191939597607879</v>
       </c>
       <c r="T79">
-        <v>3.599745947175274</v>
+        <v>3.763370762955968</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0660996636897055</v>
+        <v>0.06525223210394004</v>
       </c>
       <c r="W79">
-        <v>0.2202136993019674</v>
+        <v>0.2204135236698909</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2754152653737729</v>
+        <v>0.2718843004330835</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2421452196098883</v>
+        <v>0.2440452196098883</v>
       </c>
       <c r="C80">
-        <v>-247.0497410345483</v>
+        <v>-253.9878888463801</v>
       </c>
       <c r="D80">
-        <v>159.7232406910214</v>
+        <v>158.1924387987482</v>
       </c>
       <c r="E80">
-        <v>27.13838976971107</v>
+        <v>32.54573568926969</v>
       </c>
       <c r="F80">
-        <v>421.7729817255697</v>
+        <v>427.1803276451283</v>
       </c>
       <c r="G80">
         <v>15</v>
@@ -7835,37 +7835,37 @@
         <v>27.04</v>
       </c>
       <c r="M80">
-        <v>99.45406909088933</v>
+        <v>100.7291212587213</v>
       </c>
       <c r="N80">
-        <v>-72.41406909088933</v>
+        <v>-73.68912125872126</v>
       </c>
       <c r="O80">
-        <v>-17.37937658181344</v>
+        <v>-17.6853891020931</v>
       </c>
       <c r="P80">
-        <v>-55.03469250907589</v>
+        <v>-56.00373215662816</v>
       </c>
       <c r="Q80">
-        <v>-54.79469250907589</v>
+        <v>-55.76373215662816</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3191939597607879</v>
+        <v>0.3322127197493969</v>
       </c>
       <c r="T80">
-        <v>3.763370762955968</v>
+        <v>3.9425788945253</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06525223210394004</v>
+        <v>0.06442625448237117</v>
       </c>
       <c r="W80">
-        <v>0.2204135236698909</v>
+        <v>0.2206082891930569</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2718843004330835</v>
+        <v>0.2684427270098799</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2440452196098883</v>
+        <v>0.2459452196098883</v>
       </c>
       <c r="C81">
-        <v>-253.9878888463801</v>
+        <v>-260.8969725256687</v>
       </c>
       <c r="D81">
-        <v>158.1924387987482</v>
+        <v>156.6907010390182</v>
       </c>
       <c r="E81">
-        <v>32.54573568926969</v>
+        <v>37.95308160882826</v>
       </c>
       <c r="F81">
-        <v>427.1803276451283</v>
+        <v>432.5876735646869</v>
       </c>
       <c r="G81">
         <v>15</v>
@@ -7917,37 +7917,37 @@
         <v>27.04</v>
       </c>
       <c r="M81">
-        <v>100.7291212587213</v>
+        <v>102.0041734265532</v>
       </c>
       <c r="N81">
-        <v>-73.68912125872126</v>
+        <v>-74.96417342655317</v>
       </c>
       <c r="O81">
-        <v>-17.6853891020931</v>
+        <v>-17.99140162237276</v>
       </c>
       <c r="P81">
-        <v>-56.00373215662816</v>
+        <v>-56.97277180418041</v>
       </c>
       <c r="Q81">
-        <v>-55.76373215662816</v>
+        <v>-56.73277180418041</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3322127197493969</v>
+        <v>0.3465333557368668</v>
       </c>
       <c r="T81">
-        <v>3.9425788945253</v>
+        <v>4.139707839251566</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06442625448237117</v>
+        <v>0.06362092630134153</v>
       </c>
       <c r="W81">
-        <v>0.2206082891930569</v>
+        <v>0.2207981855781437</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2684427270098799</v>
+        <v>0.2650871929222565</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2459452196098883</v>
+        <v>0.2478452196098883</v>
       </c>
       <c r="C82">
-        <v>-260.8969725256687</v>
+        <v>-267.7778120153745</v>
       </c>
       <c r="D82">
-        <v>156.6907010390182</v>
+        <v>155.217207468871</v>
       </c>
       <c r="E82">
-        <v>37.95308160882826</v>
+        <v>43.36042752838688</v>
       </c>
       <c r="F82">
-        <v>432.5876735646869</v>
+        <v>437.9950194842455</v>
       </c>
       <c r="G82">
         <v>15</v>
@@ -7999,37 +7999,37 @@
         <v>27.04</v>
       </c>
       <c r="M82">
-        <v>102.0041734265532</v>
+        <v>103.2792255943851</v>
       </c>
       <c r="N82">
-        <v>-74.96417342655317</v>
+        <v>-76.23922559438509</v>
       </c>
       <c r="O82">
-        <v>-17.99140162237276</v>
+        <v>-18.29741414265242</v>
       </c>
       <c r="P82">
-        <v>-56.97277180418041</v>
+        <v>-57.94181145173267</v>
       </c>
       <c r="Q82">
-        <v>-56.73277180418041</v>
+        <v>-57.70181145173267</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3465333557368668</v>
+        <v>0.3623614270914386</v>
       </c>
       <c r="T82">
-        <v>4.139707839251566</v>
+        <v>4.357587199212174</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06362092630134153</v>
+        <v>0.06283548276675707</v>
       </c>
       <c r="W82">
-        <v>0.2207981855781437</v>
+        <v>0.2209833931635987</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2650871929222565</v>
+        <v>0.2618145115281545</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2478452196098883</v>
+        <v>0.2497452196098883</v>
       </c>
       <c r="C83">
-        <v>-267.7778120153745</v>
+        <v>-274.6311967033581</v>
       </c>
       <c r="D83">
-        <v>155.217207468871</v>
+        <v>153.771168700446</v>
       </c>
       <c r="E83">
-        <v>43.36042752838688</v>
+        <v>48.76777344794544</v>
       </c>
       <c r="F83">
-        <v>437.9950194842455</v>
+        <v>443.4023654038041</v>
       </c>
       <c r="G83">
         <v>15</v>
@@ -8081,37 +8081,37 @@
         <v>27.04</v>
       </c>
       <c r="M83">
-        <v>103.2792255943851</v>
+        <v>104.554277762217</v>
       </c>
       <c r="N83">
-        <v>-76.23922559438509</v>
+        <v>-77.51427776221701</v>
       </c>
       <c r="O83">
-        <v>-18.29741414265242</v>
+        <v>-18.60342666293208</v>
       </c>
       <c r="P83">
-        <v>-57.94181145173267</v>
+        <v>-58.91085109928493</v>
       </c>
       <c r="Q83">
-        <v>-57.70181145173267</v>
+        <v>-58.67085109928492</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3623614270914386</v>
+        <v>0.3799481730409631</v>
       </c>
       <c r="T83">
-        <v>4.357587199212174</v>
+        <v>4.599675376946185</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06283548276675707</v>
+        <v>0.06206919639155271</v>
       </c>
       <c r="W83">
-        <v>0.2209833931635987</v>
+        <v>0.2211640834908719</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2618145115281545</v>
+        <v>0.2586216516314697</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2497452196098883</v>
+        <v>0.2516452196098883</v>
       </c>
       <c r="C84">
-        <v>-274.6311967033581</v>
+        <v>-281.4578868325348</v>
       </c>
       <c r="D84">
-        <v>153.771168700446</v>
+        <v>152.351824490828</v>
       </c>
       <c r="E84">
-        <v>48.76777344794544</v>
+        <v>54.17511936750407</v>
       </c>
       <c r="F84">
-        <v>443.4023654038041</v>
+        <v>448.8097113233627</v>
       </c>
       <c r="G84">
         <v>15</v>
@@ -8163,37 +8163,37 @@
         <v>27.04</v>
       </c>
       <c r="M84">
-        <v>104.554277762217</v>
+        <v>105.8293299300489</v>
       </c>
       <c r="N84">
-        <v>-77.51427776221701</v>
+        <v>-78.78932993004892</v>
       </c>
       <c r="O84">
-        <v>-18.60342666293208</v>
+        <v>-18.90943918321174</v>
       </c>
       <c r="P84">
-        <v>-58.91085109928493</v>
+        <v>-59.87989074683718</v>
       </c>
       <c r="Q84">
-        <v>-58.67085109928492</v>
+        <v>-59.63989074683717</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3799481730409631</v>
+        <v>0.3996039479257256</v>
       </c>
       <c r="T84">
-        <v>4.599675376946185</v>
+        <v>4.870244516766549</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06206919639155271</v>
+        <v>0.061321374748281</v>
       </c>
       <c r="W84">
-        <v>0.2211640834908719</v>
+        <v>0.2213404198343553</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2586216516314697</v>
+        <v>0.2555057281178376</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2516452196098883</v>
+        <v>0.2535452196098883</v>
       </c>
       <c r="C85">
-        <v>-281.4578868325348</v>
+        <v>-288.2586148336456</v>
       </c>
       <c r="D85">
-        <v>152.351824490828</v>
+        <v>150.9584424092757</v>
       </c>
       <c r="E85">
-        <v>54.17511936750407</v>
+        <v>59.58246528706263</v>
       </c>
       <c r="F85">
-        <v>448.8097113233627</v>
+        <v>454.2170572429213</v>
       </c>
       <c r="G85">
         <v>15</v>
@@ -8245,37 +8245,37 @@
         <v>27.04</v>
       </c>
       <c r="M85">
-        <v>105.8293299300489</v>
+        <v>107.1043820978808</v>
       </c>
       <c r="N85">
-        <v>-78.78932993004892</v>
+        <v>-80.06438209788084</v>
       </c>
       <c r="O85">
-        <v>-18.90943918321174</v>
+        <v>-19.2154517034914</v>
       </c>
       <c r="P85">
-        <v>-59.87989074683718</v>
+        <v>-60.84893039438944</v>
       </c>
       <c r="Q85">
-        <v>-59.63989074683717</v>
+        <v>-60.60893039438944</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3996039479257256</v>
+        <v>0.4217166946710835</v>
       </c>
       <c r="T85">
-        <v>4.870244516766549</v>
+        <v>5.174634799064459</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.061321374748281</v>
+        <v>0.06059135838223003</v>
       </c>
       <c r="W85">
-        <v>0.2213404198343553</v>
+        <v>0.2215125576934702</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2555057281178376</v>
+        <v>0.2524639932592918</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2535452196098883</v>
+        <v>0.2554452196098883</v>
       </c>
       <c r="C86">
-        <v>-288.2586148336455</v>
+        <v>-295.0340865855572</v>
       </c>
       <c r="D86">
-        <v>150.9584424092757</v>
+        <v>149.5903165769226</v>
       </c>
       <c r="E86">
-        <v>59.58246528706258</v>
+        <v>64.98981120662114</v>
       </c>
       <c r="F86">
-        <v>454.2170572429212</v>
+        <v>459.6244031624798</v>
       </c>
       <c r="G86">
         <v>15</v>
@@ -8327,37 +8327,37 @@
         <v>27.04</v>
       </c>
       <c r="M86">
-        <v>107.1043820978808</v>
+        <v>108.3794342657127</v>
       </c>
       <c r="N86">
-        <v>-80.06438209788082</v>
+        <v>-81.33943426571273</v>
       </c>
       <c r="O86">
-        <v>-19.2154517034914</v>
+        <v>-19.52146422377105</v>
       </c>
       <c r="P86">
-        <v>-60.84893039438943</v>
+        <v>-61.81797004194167</v>
       </c>
       <c r="Q86">
-        <v>-60.60893039438943</v>
+        <v>-61.57797004194167</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4217166946710832</v>
+        <v>0.4467778076491555</v>
       </c>
       <c r="T86">
-        <v>5.174634799064455</v>
+        <v>5.519610452335419</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06059135838223003</v>
+        <v>0.05987851887185087</v>
       </c>
       <c r="W86">
-        <v>0.2215125576934702</v>
+        <v>0.2216806452500176</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2524639932592919</v>
+        <v>0.249493828632712</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2554452196098883</v>
+        <v>0.2573452196098883</v>
       </c>
       <c r="C87">
-        <v>-295.0340865855572</v>
+        <v>-301.7849826076438</v>
       </c>
       <c r="D87">
-        <v>149.5903165769226</v>
+        <v>148.2467664743947</v>
       </c>
       <c r="E87">
-        <v>64.98981120662114</v>
+        <v>70.39715712617976</v>
       </c>
       <c r="F87">
-        <v>459.6244031624798</v>
+        <v>465.0317490820384</v>
       </c>
       <c r="G87">
         <v>15</v>
@@ -8409,37 +8409,37 @@
         <v>27.04</v>
       </c>
       <c r="M87">
-        <v>108.3794342657127</v>
+        <v>109.6544864335447</v>
       </c>
       <c r="N87">
-        <v>-81.33943426571273</v>
+        <v>-82.61448643354466</v>
       </c>
       <c r="O87">
-        <v>-19.52146422377105</v>
+        <v>-19.82747674405072</v>
       </c>
       <c r="P87">
-        <v>-61.81797004194167</v>
+        <v>-62.78700968949394</v>
       </c>
       <c r="Q87">
-        <v>-61.57797004194167</v>
+        <v>-62.54700968949394</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4467778076491555</v>
+        <v>0.4754190796240952</v>
       </c>
       <c r="T87">
-        <v>5.519610452335419</v>
+        <v>5.91386834178795</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05987851887185087</v>
+        <v>0.05918225702450376</v>
       </c>
       <c r="W87">
-        <v>0.2216806452500176</v>
+        <v>0.221844823793622</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.249493828632712</v>
+        <v>0.246592737602099</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2573452196098883</v>
+        <v>0.2592452196098882</v>
       </c>
       <c r="C88">
-        <v>-301.7849826076438</v>
+        <v>-308.5119591884846</v>
       </c>
       <c r="D88">
-        <v>148.2467664743947</v>
+        <v>146.9271358131124</v>
       </c>
       <c r="E88">
-        <v>70.39715712617976</v>
+        <v>75.80450304573833</v>
       </c>
       <c r="F88">
-        <v>465.0317490820384</v>
+        <v>470.439095001597</v>
       </c>
       <c r="G88">
         <v>15</v>
@@ -8491,37 +8491,37 @@
         <v>27.04</v>
       </c>
       <c r="M88">
-        <v>109.6544864335447</v>
+        <v>110.9295386013766</v>
       </c>
       <c r="N88">
-        <v>-82.61448643354466</v>
+        <v>-83.88953860137656</v>
       </c>
       <c r="O88">
-        <v>-19.82747674405072</v>
+        <v>-20.13348926433037</v>
       </c>
       <c r="P88">
-        <v>-62.78700968949394</v>
+        <v>-63.75604933704619</v>
       </c>
       <c r="Q88">
-        <v>-62.54700968949394</v>
+        <v>-63.51604933704618</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4754190796240952</v>
+        <v>0.5084667011336409</v>
       </c>
       <c r="T88">
-        <v>5.91386834178795</v>
+        <v>6.368781291156253</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05918225702450376</v>
+        <v>0.05850200119663591</v>
       </c>
       <c r="W88">
-        <v>0.221844823793622</v>
+        <v>0.2220052281178332</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.246592737602099</v>
+        <v>0.2437583383193163</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2592452196098882</v>
+        <v>0.2611452196098883</v>
       </c>
       <c r="C89">
-        <v>-308.5119591884846</v>
+        <v>-315.2156494548118</v>
       </c>
       <c r="D89">
-        <v>146.9271358131124</v>
+        <v>145.6307914663438</v>
       </c>
       <c r="E89">
-        <v>75.80450304573833</v>
+        <v>81.21184896529695</v>
       </c>
       <c r="F89">
-        <v>470.439095001597</v>
+        <v>475.8464409211556</v>
       </c>
       <c r="G89">
         <v>15</v>
@@ -8573,37 +8573,37 @@
         <v>27.04</v>
       </c>
       <c r="M89">
-        <v>110.9295386013766</v>
+        <v>112.2045907692085</v>
       </c>
       <c r="N89">
-        <v>-83.88953860137656</v>
+        <v>-85.16459076920849</v>
       </c>
       <c r="O89">
-        <v>-20.13348926433037</v>
+        <v>-20.43950178461004</v>
       </c>
       <c r="P89">
-        <v>-63.75604933704619</v>
+        <v>-64.72508898459844</v>
       </c>
       <c r="Q89">
-        <v>-63.51604933704618</v>
+        <v>-64.48508898459845</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5084667011336409</v>
+        <v>0.5470222595614445</v>
       </c>
       <c r="T89">
-        <v>6.368781291156253</v>
+        <v>6.899513065419276</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05850200119663591</v>
+        <v>0.0578372057284923</v>
       </c>
       <c r="W89">
-        <v>0.2220052281178332</v>
+        <v>0.2221619868892215</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2437583383193163</v>
+        <v>0.2409883572020514</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2611452196098883</v>
+        <v>0.2630452196098882</v>
       </c>
       <c r="C90">
-        <v>-315.2156494548118</v>
+        <v>-321.8966643843625</v>
       </c>
       <c r="D90">
-        <v>145.6307914663438</v>
+        <v>144.3571224563516</v>
       </c>
       <c r="E90">
-        <v>81.21184896529695</v>
+        <v>86.61919488485552</v>
       </c>
       <c r="F90">
-        <v>475.8464409211556</v>
+        <v>481.2537868407142</v>
       </c>
       <c r="G90">
         <v>15</v>
@@ -8655,37 +8655,37 @@
         <v>27.04</v>
       </c>
       <c r="M90">
-        <v>112.2045907692085</v>
+        <v>113.4796429370404</v>
       </c>
       <c r="N90">
-        <v>-85.16459076920849</v>
+        <v>-86.43964293704039</v>
       </c>
       <c r="O90">
-        <v>-20.43950178461004</v>
+        <v>-20.74551430488969</v>
       </c>
       <c r="P90">
-        <v>-64.72508898459844</v>
+        <v>-65.69412863215069</v>
       </c>
       <c r="Q90">
-        <v>-64.48508898459845</v>
+        <v>-65.4541286321507</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5470222595614445</v>
+        <v>0.5925879195215757</v>
       </c>
       <c r="T90">
-        <v>6.899513065419276</v>
+        <v>7.526741525911937</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0578372057284923</v>
+        <v>0.05718734948435195</v>
       </c>
       <c r="W90">
-        <v>0.2221619868892215</v>
+        <v>0.2223152229915898</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2409883572020514</v>
+        <v>0.2382806228514665</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2630452196098882</v>
+        <v>0.2649452196098883</v>
       </c>
       <c r="C91">
-        <v>-321.8966643843625</v>
+        <v>-328.5555937660442</v>
       </c>
       <c r="D91">
-        <v>144.3571224563516</v>
+        <v>143.1055389942285</v>
       </c>
       <c r="E91">
-        <v>86.61919488485552</v>
+        <v>92.02654080441414</v>
       </c>
       <c r="F91">
-        <v>481.2537868407142</v>
+        <v>486.6611327602728</v>
       </c>
       <c r="G91">
         <v>15</v>
@@ -8737,37 +8737,37 @@
         <v>27.04</v>
       </c>
       <c r="M91">
-        <v>113.4796429370404</v>
+        <v>114.7546951048723</v>
       </c>
       <c r="N91">
-        <v>-86.43964293704039</v>
+        <v>-87.71469510487232</v>
       </c>
       <c r="O91">
-        <v>-20.74551430488969</v>
+        <v>-21.05152682516936</v>
       </c>
       <c r="P91">
-        <v>-65.69412863215069</v>
+        <v>-66.66316827970296</v>
       </c>
       <c r="Q91">
-        <v>-65.4541286321507</v>
+        <v>-66.42316827970296</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5925879195215757</v>
+        <v>0.6472667114737335</v>
       </c>
       <c r="T91">
-        <v>7.526741525911937</v>
+        <v>8.279415678503133</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05718734948435195</v>
+        <v>0.05655193449008136</v>
       </c>
       <c r="W91">
-        <v>0.2223152229915898</v>
+        <v>0.2224650538472388</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2382806228514665</v>
+        <v>0.235633060375339</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2649452196098883</v>
+        <v>0.2668452196098883</v>
       </c>
       <c r="C92">
-        <v>-328.5555937660442</v>
+        <v>-335.19300711058</v>
       </c>
       <c r="D92">
-        <v>143.1055389942285</v>
+        <v>141.8754715692514</v>
       </c>
       <c r="E92">
-        <v>92.02654080441414</v>
+        <v>97.43388672397271</v>
       </c>
       <c r="F92">
-        <v>486.6611327602728</v>
+        <v>492.0684786798313</v>
       </c>
       <c r="G92">
         <v>15</v>
@@ -8819,37 +8819,37 @@
         <v>27.04</v>
       </c>
       <c r="M92">
-        <v>114.7546951048723</v>
+        <v>116.0297472727042</v>
       </c>
       <c r="N92">
-        <v>-87.71469510487232</v>
+        <v>-88.98974727270424</v>
       </c>
       <c r="O92">
-        <v>-21.05152682516936</v>
+        <v>-21.35753934544902</v>
       </c>
       <c r="P92">
-        <v>-66.66316827970296</v>
+        <v>-67.63220792725522</v>
       </c>
       <c r="Q92">
-        <v>-66.42316827970296</v>
+        <v>-67.39220792725523</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6472667114737335</v>
+        <v>0.7140963460819261</v>
       </c>
       <c r="T92">
-        <v>8.279415678503133</v>
+        <v>9.19935075389237</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05655193449008136</v>
+        <v>0.05593048466052003</v>
       </c>
       <c r="W92">
-        <v>0.2224650538472388</v>
+        <v>0.2226115917170494</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.235633060375339</v>
+        <v>0.2330436860855002</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2668452196098883</v>
+        <v>0.2687452196098883</v>
       </c>
       <c r="C93">
-        <v>-335.19300711058</v>
+        <v>-341.8094545145896</v>
       </c>
       <c r="D93">
-        <v>141.8754715692514</v>
+        <v>140.6663700848004</v>
       </c>
       <c r="E93">
-        <v>97.43388672397271</v>
+        <v>102.8412326435313</v>
       </c>
       <c r="F93">
-        <v>492.0684786798313</v>
+        <v>497.47582459939</v>
       </c>
       <c r="G93">
         <v>15</v>
@@ -8901,37 +8901,37 @@
         <v>27.04</v>
       </c>
       <c r="M93">
-        <v>116.0297472727042</v>
+        <v>117.3047994405362</v>
       </c>
       <c r="N93">
-        <v>-88.98974727270424</v>
+        <v>-90.26479944053615</v>
       </c>
       <c r="O93">
-        <v>-21.35753934544902</v>
+        <v>-21.66355186572867</v>
       </c>
       <c r="P93">
-        <v>-67.63220792725522</v>
+        <v>-68.60124757480747</v>
       </c>
       <c r="Q93">
-        <v>-67.39220792725523</v>
+        <v>-68.36124757480748</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7140963460819261</v>
+        <v>0.797633389342167</v>
       </c>
       <c r="T93">
-        <v>9.19935075389237</v>
+        <v>10.34926959812892</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05593048466052003</v>
+        <v>0.0553225446098622</v>
       </c>
       <c r="W93">
-        <v>0.2226115917170494</v>
+        <v>0.2227549439809945</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2330436860855002</v>
+        <v>0.2305106025410926</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2687452196098883</v>
+        <v>0.2706452196098882</v>
       </c>
       <c r="C94">
-        <v>-341.8094545145896</v>
+        <v>-348.4054674808606</v>
       </c>
       <c r="D94">
-        <v>140.6663700848004</v>
+        <v>139.4777030380879</v>
       </c>
       <c r="E94">
-        <v>102.8412326435313</v>
+        <v>108.2485785630899</v>
       </c>
       <c r="F94">
-        <v>497.47582459939</v>
+        <v>502.8831705189485</v>
       </c>
       <c r="G94">
         <v>15</v>
@@ -8983,37 +8983,37 @@
         <v>27.04</v>
       </c>
       <c r="M94">
-        <v>117.3047994405362</v>
+        <v>118.5798516083681</v>
       </c>
       <c r="N94">
-        <v>-90.26479944053615</v>
+        <v>-91.53985160836807</v>
       </c>
       <c r="O94">
-        <v>-21.66355186572867</v>
+        <v>-21.96956438600834</v>
       </c>
       <c r="P94">
-        <v>-68.60124757480747</v>
+        <v>-69.57028722235972</v>
       </c>
       <c r="Q94">
-        <v>-68.36124757480748</v>
+        <v>-69.33028722235973</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.797633389342167</v>
+        <v>0.9050381592481909</v>
       </c>
       <c r="T94">
-        <v>10.34926959812892</v>
+        <v>11.82773668357591</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0553225446098622</v>
+        <v>0.05472767853878842</v>
       </c>
       <c r="W94">
-        <v>0.2227549439809945</v>
+        <v>0.2228952134005537</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2305106025410926</v>
+        <v>0.2280319939116184</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2706452196098882</v>
+        <v>0.2725452196098883</v>
       </c>
       <c r="C95">
-        <v>-348.4054674808606</v>
+        <v>-354.981559697379</v>
       </c>
       <c r="D95">
-        <v>139.4777030380879</v>
+        <v>138.3089567411281</v>
       </c>
       <c r="E95">
-        <v>108.2485785630899</v>
+        <v>113.6559244826485</v>
       </c>
       <c r="F95">
-        <v>502.8831705189485</v>
+        <v>508.2905164385071</v>
       </c>
       <c r="G95">
         <v>15</v>
@@ -9065,37 +9065,37 @@
         <v>27.04</v>
       </c>
       <c r="M95">
-        <v>118.5798516083681</v>
+        <v>119.8549037762</v>
       </c>
       <c r="N95">
-        <v>-91.53985160836807</v>
+        <v>-92.81490377619997</v>
       </c>
       <c r="O95">
-        <v>-21.96956438600834</v>
+        <v>-22.27557690628799</v>
       </c>
       <c r="P95">
-        <v>-69.57028722235972</v>
+        <v>-70.53932686991197</v>
       </c>
       <c r="Q95">
-        <v>-69.33028722235973</v>
+        <v>-70.29932686991198</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9050381592481909</v>
+        <v>1.04824451912289</v>
       </c>
       <c r="T95">
-        <v>11.82773668357591</v>
+        <v>13.79902613083856</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05472767853878842</v>
+        <v>0.0541454691926311</v>
       </c>
       <c r="W95">
-        <v>0.2228952134005537</v>
+        <v>0.2230324983643776</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2280319939116184</v>
+        <v>0.2256061216359629</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2725452196098883</v>
+        <v>0.2744452196098883</v>
       </c>
       <c r="C96">
-        <v>-354.981559697379</v>
+        <v>-361.5382277775167</v>
       </c>
       <c r="D96">
-        <v>138.3089567411281</v>
+        <v>137.1596345805489</v>
       </c>
       <c r="E96">
-        <v>113.6559244826485</v>
+        <v>119.063270402207</v>
       </c>
       <c r="F96">
-        <v>508.2905164385071</v>
+        <v>513.6978623580657</v>
       </c>
       <c r="G96">
         <v>15</v>
@@ -9147,37 +9147,37 @@
         <v>27.04</v>
       </c>
       <c r="M96">
-        <v>119.8549037762</v>
+        <v>121.1299559440319</v>
       </c>
       <c r="N96">
-        <v>-92.81490377619997</v>
+        <v>-94.08995594403189</v>
       </c>
       <c r="O96">
-        <v>-22.27557690628799</v>
+        <v>-22.58158942656765</v>
       </c>
       <c r="P96">
-        <v>-70.53932686991197</v>
+        <v>-71.50836651746422</v>
       </c>
       <c r="Q96">
-        <v>-70.29932686991198</v>
+        <v>-71.26836651746423</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.04824451912289</v>
+        <v>1.248733422947468</v>
       </c>
       <c r="T96">
-        <v>13.79902613083856</v>
+        <v>16.55883135700628</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0541454691926311</v>
+        <v>0.05357551688534024</v>
       </c>
       <c r="W96">
-        <v>0.2230324983643776</v>
+        <v>0.2231668931184368</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2256061216359629</v>
+        <v>0.2232313203555844</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2744452196098883</v>
+        <v>0.2763452196098883</v>
       </c>
       <c r="C97">
-        <v>-361.5382277775167</v>
+        <v>-368.0759519636212</v>
       </c>
       <c r="D97">
-        <v>137.1596345805489</v>
+        <v>136.0292563140031</v>
       </c>
       <c r="E97">
-        <v>119.063270402207</v>
+        <v>124.4706163217657</v>
       </c>
       <c r="F97">
-        <v>513.6978623580657</v>
+        <v>519.1052082776243</v>
       </c>
       <c r="G97">
         <v>15</v>
@@ -9229,37 +9229,37 @@
         <v>27.04</v>
       </c>
       <c r="M97">
-        <v>121.1299559440319</v>
+        <v>122.4050081118638</v>
       </c>
       <c r="N97">
-        <v>-94.08995594403189</v>
+        <v>-95.36500811186382</v>
       </c>
       <c r="O97">
-        <v>-22.58158942656765</v>
+        <v>-22.88760194684732</v>
       </c>
       <c r="P97">
-        <v>-71.50836651746422</v>
+        <v>-72.4774061650165</v>
       </c>
       <c r="Q97">
-        <v>-71.26836651746423</v>
+        <v>-72.23740616501651</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.248733422947468</v>
+        <v>1.549466778684336</v>
       </c>
       <c r="T97">
-        <v>16.55883135700628</v>
+        <v>20.69853919625787</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05357551688534024</v>
+        <v>0.05301743858445128</v>
       </c>
       <c r="W97">
-        <v>0.2231668931184368</v>
+        <v>0.2232984879817864</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2232313203555844</v>
+        <v>0.2209059941018804</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2763452196098883</v>
+        <v>0.2782452196098882</v>
       </c>
       <c r="C98">
-        <v>-368.0759519636211</v>
+        <v>-374.5951967960949</v>
       </c>
       <c r="D98">
-        <v>136.0292563140031</v>
+        <v>134.9173574010879</v>
       </c>
       <c r="E98">
-        <v>124.4706163217656</v>
+        <v>129.8779622413242</v>
       </c>
       <c r="F98">
-        <v>519.1052082776242</v>
+        <v>524.5125541971828</v>
       </c>
       <c r="G98">
         <v>15</v>
@@ -9311,37 +9311,37 @@
         <v>27.04</v>
       </c>
       <c r="M98">
-        <v>122.4050081118638</v>
+        <v>123.6800602796957</v>
       </c>
       <c r="N98">
-        <v>-95.36500811186379</v>
+        <v>-96.6400602796957</v>
       </c>
       <c r="O98">
-        <v>-22.88760194684731</v>
+        <v>-23.19361446712697</v>
       </c>
       <c r="P98">
-        <v>-72.47740616501648</v>
+        <v>-73.44644581256874</v>
       </c>
       <c r="Q98">
-        <v>-72.23740616501648</v>
+        <v>-73.20644581256875</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.549466778684332</v>
+        <v>2.050689038245776</v>
       </c>
       <c r="T98">
-        <v>20.69853919625781</v>
+        <v>27.59805226167708</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05301743858445129</v>
+        <v>0.05247086705265282</v>
       </c>
       <c r="W98">
-        <v>0.2232984879817864</v>
+        <v>0.2234273695489845</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2209059941018804</v>
+        <v>0.2186286127193868</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2782452196098882</v>
+        <v>0.2801452196098883</v>
       </c>
       <c r="C99">
-        <v>-374.5951967960949</v>
+        <v>-381.0964117499306</v>
       </c>
       <c r="D99">
-        <v>134.9173574010879</v>
+        <v>133.8234883668109</v>
       </c>
       <c r="E99">
-        <v>129.8779622413242</v>
+        <v>135.2853081608828</v>
       </c>
       <c r="F99">
-        <v>524.5125541971828</v>
+        <v>529.9199001167415</v>
       </c>
       <c r="G99">
         <v>15</v>
@@ -9393,37 +9393,37 @@
         <v>27.04</v>
       </c>
       <c r="M99">
-        <v>123.6800602796957</v>
+        <v>124.9551124475276</v>
       </c>
       <c r="N99">
-        <v>-96.6400602796957</v>
+        <v>-97.91511244752763</v>
       </c>
       <c r="O99">
-        <v>-23.19361446712697</v>
+        <v>-23.49962698740663</v>
       </c>
       <c r="P99">
-        <v>-73.44644581256874</v>
+        <v>-74.415485460121</v>
       </c>
       <c r="Q99">
-        <v>-73.20644581256875</v>
+        <v>-74.17548546012101</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.050689038245776</v>
+        <v>3.053133557368664</v>
       </c>
       <c r="T99">
-        <v>27.59805226167708</v>
+        <v>41.39707839251562</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05247086705265282</v>
+        <v>0.05193545004191145</v>
       </c>
       <c r="W99">
-        <v>0.2234273695489845</v>
+        <v>0.2235536208801173</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2186286127193868</v>
+        <v>0.2163977085079645</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2801452196098883</v>
+        <v>0.2820452196098883</v>
       </c>
       <c r="C100">
-        <v>-381.0964117499306</v>
+        <v>-387.5800318405254</v>
       </c>
       <c r="D100">
-        <v>133.8234883668109</v>
+        <v>132.7472141957746</v>
       </c>
       <c r="E100">
-        <v>135.2853081608828</v>
+        <v>140.6926540804414</v>
       </c>
       <c r="F100">
-        <v>529.9199001167415</v>
+        <v>535.3272460363</v>
       </c>
       <c r="G100">
         <v>15</v>
@@ -9475,37 +9475,37 @@
         <v>27.04</v>
       </c>
       <c r="M100">
-        <v>124.9551124475276</v>
+        <v>126.2301646153596</v>
       </c>
       <c r="N100">
-        <v>-97.91511244752763</v>
+        <v>-99.19016461535955</v>
       </c>
       <c r="O100">
-        <v>-23.49962698740663</v>
+        <v>-23.80563950768629</v>
       </c>
       <c r="P100">
-        <v>-74.415485460121</v>
+        <v>-75.38452510767326</v>
       </c>
       <c r="Q100">
-        <v>-74.17548546012101</v>
+        <v>-75.14452510767326</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.053133557368664</v>
+        <v>6.060467114737328</v>
       </c>
       <c r="T100">
-        <v>41.39707839251562</v>
+        <v>82.79415678503123</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05193545004191145</v>
+        <v>0.0514108495364376</v>
       </c>
       <c r="W100">
-        <v>0.2235536208801173</v>
+        <v>0.223677321679308</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2163977085079645</v>
+        <v>0.2142118730684901</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2820452196098883</v>
-      </c>
-      <c r="C101">
-        <v>-387.5800318405254</v>
-      </c>
-      <c r="D101">
-        <v>132.7472141957746</v>
-      </c>
-      <c r="E101">
-        <v>140.6926540804414</v>
-      </c>
-      <c r="F101">
-        <v>535.3272460363</v>
-      </c>
-      <c r="G101">
-        <v>15</v>
-      </c>
-      <c r="H101">
-        <v>146.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>27.28</v>
-      </c>
-      <c r="K101">
-        <v>0.2399999999999993</v>
-      </c>
-      <c r="L101">
-        <v>27.04</v>
-      </c>
-      <c r="M101">
-        <v>126.2301646153596</v>
-      </c>
-      <c r="N101">
-        <v>-99.19016461535955</v>
-      </c>
-      <c r="O101">
-        <v>-23.80563950768629</v>
-      </c>
-      <c r="P101">
-        <v>-75.38452510767326</v>
-      </c>
-      <c r="Q101">
-        <v>-75.14452510767326</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.060467114737328</v>
-      </c>
-      <c r="T101">
-        <v>82.79415678503123</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0514108495364376</v>
-      </c>
-      <c r="W101">
-        <v>0.223677321679308</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2142118730684901</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
